--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
@@ -211,7 +211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +223,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,37 +248,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -678,49 +650,49 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>2.3175139691317629E-2</v>
+        <v>2.45213213053645E-2</v>
       </c>
       <c r="C2">
-        <v>3.5995181287556972E-2</v>
+        <v>3.6009367228646887E-2</v>
       </c>
       <c r="D2">
-        <v>4.4265873662314603E-2</v>
+        <v>4.4235671134611132E-2</v>
       </c>
       <c r="E2">
-        <v>5.2373942067479473E-2</v>
+        <v>5.1703411367836183E-2</v>
       </c>
       <c r="F2">
-        <v>9.892692700270822E-2</v>
+        <v>9.6456364521967042E-2</v>
       </c>
       <c r="G2">
-        <v>8.2154548779842629E-2</v>
+        <v>8.1015777899707597E-2</v>
       </c>
       <c r="H2">
-        <v>9.7447804916191538E-2</v>
+        <v>9.532868542804751E-2</v>
       </c>
       <c r="I2">
-        <v>0.1416849244109015</v>
+        <v>0.1378374972320664</v>
       </c>
       <c r="J2">
-        <v>0.1304800912395947</v>
+        <v>0.12809607773988491</v>
       </c>
       <c r="K2">
-        <v>0.1550555715967846</v>
+        <v>0.15277521815634559</v>
       </c>
       <c r="L2">
-        <v>0.1825713877482272</v>
+        <v>0.18050541400866979</v>
       </c>
       <c r="M2">
-        <v>0.23610336253472111</v>
+        <v>0.22854696902232299</v>
       </c>
       <c r="N2">
-        <v>0.31809009950527889</v>
+        <v>0.31484120443508212</v>
       </c>
       <c r="O2">
-        <v>0.38621081400346691</v>
+        <v>0.37968198703154937</v>
       </c>
       <c r="P2">
-        <v>0.42757118759323748</v>
+        <v>0.42075244978898668</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -728,49 +700,49 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>4.0481560623676693E-2</v>
+        <v>3.8577989308622107E-2</v>
       </c>
       <c r="C3">
-        <v>3.6807116048118822E-2</v>
+        <v>3.7406487672083211E-2</v>
       </c>
       <c r="D3">
-        <v>6.5051422859737973E-2</v>
+        <v>6.6182588410944376E-2</v>
       </c>
       <c r="E3">
-        <v>0.1570267106160447</v>
+        <v>0.1559745947009806</v>
       </c>
       <c r="F3">
-        <v>0.14476248223098059</v>
+        <v>0.13991770553698499</v>
       </c>
       <c r="G3">
-        <v>0.16972585242399349</v>
+        <v>0.1655356754552606</v>
       </c>
       <c r="H3">
-        <v>0.23982723804035311</v>
+        <v>0.23803987717491931</v>
       </c>
       <c r="I3">
-        <v>0.26922315536606001</v>
+        <v>0.26825646603021358</v>
       </c>
       <c r="J3">
-        <v>0.33253696049654269</v>
+        <v>0.33522299233580499</v>
       </c>
       <c r="K3">
-        <v>0.36605200091211892</v>
+        <v>0.37155324443023202</v>
       </c>
       <c r="L3">
-        <v>0.41397262146221347</v>
+        <v>0.42019822091252867</v>
       </c>
       <c r="M3">
-        <v>0.46846235079957771</v>
+        <v>0.47622525791940851</v>
       </c>
       <c r="N3">
-        <v>0.52156595706056863</v>
+        <v>0.53460137062539714</v>
       </c>
       <c r="O3">
-        <v>0.5355711761910793</v>
+        <v>0.54680205133378557</v>
       </c>
       <c r="P3">
-        <v>0.53316532858773491</v>
+        <v>0.5427024272005625</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -778,49 +750,49 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>2.3489336736709891E-2</v>
+        <v>2.258606246832684E-2</v>
       </c>
       <c r="C4">
-        <v>3.4208726923492187E-2</v>
+        <v>3.362951467201436E-2</v>
       </c>
       <c r="D4">
-        <v>4.5080161958677589E-2</v>
+        <v>4.4290826110612969E-2</v>
       </c>
       <c r="E4">
-        <v>6.2386883028759048E-2</v>
+        <v>6.3443598343427166E-2</v>
       </c>
       <c r="F4">
-        <v>9.3799548070401473E-2</v>
+        <v>9.5682028556264731E-2</v>
       </c>
       <c r="G4">
-        <v>8.2901749934180757E-2</v>
+        <v>8.3113513888668278E-2</v>
       </c>
       <c r="H4">
-        <v>9.3520433480830167E-2</v>
+        <v>9.3281673518419095E-2</v>
       </c>
       <c r="I4">
-        <v>0.118397680047177</v>
+        <v>0.1198147676038975</v>
       </c>
       <c r="J4">
-        <v>0.1655331673223315</v>
+        <v>0.1637998153464395</v>
       </c>
       <c r="K4">
-        <v>0.20853489059058569</v>
+        <v>0.21676301846459911</v>
       </c>
       <c r="L4">
-        <v>0.25308349785395379</v>
+        <v>0.25925727193650833</v>
       </c>
       <c r="M4">
-        <v>0.32771593197419241</v>
+        <v>0.33936204764659172</v>
       </c>
       <c r="N4">
-        <v>0.39476209009141089</v>
+        <v>0.4044073407900699</v>
       </c>
       <c r="O4">
-        <v>0.43853953404390889</v>
+        <v>0.44939557874991881</v>
       </c>
       <c r="P4">
-        <v>0.48512732479966109</v>
+        <v>0.49307452792150391</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -828,49 +800,49 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.275607363153942E-2</v>
+        <v>2.154971411649154E-2</v>
       </c>
       <c r="C5">
-        <v>5.1226014004407738E-2</v>
+        <v>5.0226310015631707E-2</v>
       </c>
       <c r="D5">
-        <v>6.090959542005403E-2</v>
+        <v>6.0966171994775047E-2</v>
       </c>
       <c r="E5">
-        <v>9.9838841480959672E-2</v>
+        <v>0.10067236235072551</v>
       </c>
       <c r="F5">
-        <v>0.1194574055111385</v>
+        <v>0.1206391937768949</v>
       </c>
       <c r="G5">
-        <v>0.13112359596792311</v>
+        <v>0.13425290819344221</v>
       </c>
       <c r="H5">
-        <v>0.15700331096352649</v>
+        <v>0.15875881393545899</v>
       </c>
       <c r="I5">
-        <v>0.21495371388199319</v>
+        <v>0.21688514737115691</v>
       </c>
       <c r="J5">
-        <v>0.31502680775494218</v>
+        <v>0.31596415794511368</v>
       </c>
       <c r="K5">
-        <v>0.37426973851165002</v>
+        <v>0.37300665045240139</v>
       </c>
       <c r="L5">
-        <v>0.42588143283088198</v>
+        <v>0.42906123203252139</v>
       </c>
       <c r="M5">
-        <v>0.45243525848171767</v>
+        <v>0.44978185353122158</v>
       </c>
       <c r="N5">
-        <v>0.45944876082829089</v>
+        <v>0.45977127766185172</v>
       </c>
       <c r="O5">
-        <v>0.4718170590444728</v>
+        <v>0.47247913197700558</v>
       </c>
       <c r="P5">
-        <v>0.49112458946102427</v>
+        <v>0.49018804175776198</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -878,49 +850,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>2.1315155906236338E-2</v>
+        <v>2.001611139291137E-2</v>
       </c>
       <c r="C6">
-        <v>4.6594088934604587E-2</v>
+        <v>4.5318774408722229E-2</v>
       </c>
       <c r="D6">
-        <v>5.6714963621288812E-2</v>
+        <v>5.5947759705443523E-2</v>
       </c>
       <c r="E6">
-        <v>9.2696161483905692E-2</v>
+        <v>8.9833955701822288E-2</v>
       </c>
       <c r="F6">
-        <v>9.542489108423402E-2</v>
+        <v>9.3720788154539325E-2</v>
       </c>
       <c r="G6">
-        <v>0.10998642991403559</v>
+        <v>0.1072149710378575</v>
       </c>
       <c r="H6">
-        <v>0.1580151501635659</v>
+        <v>0.1523916278641689</v>
       </c>
       <c r="I6">
-        <v>0.1974567712261899</v>
+        <v>0.19363626189759661</v>
       </c>
       <c r="J6">
-        <v>0.2466330752111148</v>
+        <v>0.24081463191027669</v>
       </c>
       <c r="K6">
-        <v>0.27462564276531048</v>
+        <v>0.26932788717933331</v>
       </c>
       <c r="L6">
-        <v>0.32246524596326631</v>
+        <v>0.31565464383126152</v>
       </c>
       <c r="M6">
-        <v>0.36222617799721818</v>
+        <v>0.35150000395472508</v>
       </c>
       <c r="N6">
-        <v>0.39871061635247529</v>
+        <v>0.39445883243448521</v>
       </c>
       <c r="O6">
-        <v>0.4155134855486734</v>
+        <v>0.41205062676211829</v>
       </c>
       <c r="P6">
-        <v>0.43986764174612758</v>
+        <v>0.43387096346033027</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -928,49 +900,49 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>2.4303207548578731E-2</v>
+        <v>2.1646419924492451E-2</v>
       </c>
       <c r="C7">
-        <v>3.3446074587676788E-2</v>
+        <v>3.0698606256638561E-2</v>
       </c>
       <c r="D7">
-        <v>4.9976097126137153E-2</v>
+        <v>4.6204315984067823E-2</v>
       </c>
       <c r="E7">
-        <v>5.2035740235141681E-2</v>
+        <v>4.8822657980890923E-2</v>
       </c>
       <c r="F7">
-        <v>7.9326459359330692E-2</v>
+        <v>7.5750469813129939E-2</v>
       </c>
       <c r="G7">
-        <v>7.5244392727712328E-2</v>
+        <v>7.143300994472801E-2</v>
       </c>
       <c r="H7">
-        <v>0.1027343689835912</v>
+        <v>0.10229797223031491</v>
       </c>
       <c r="I7">
-        <v>0.11978667772735049</v>
+        <v>0.1181063114762408</v>
       </c>
       <c r="J7">
-        <v>0.15023690853528451</v>
+        <v>0.1468285585796992</v>
       </c>
       <c r="K7">
-        <v>0.19131453207821131</v>
+        <v>0.18593784098211119</v>
       </c>
       <c r="L7">
-        <v>0.23753046674607711</v>
+        <v>0.23438080366630301</v>
       </c>
       <c r="M7">
-        <v>0.32197454167151818</v>
+        <v>0.31861184121150871</v>
       </c>
       <c r="N7">
-        <v>0.37715966870752438</v>
+        <v>0.37347629054715348</v>
       </c>
       <c r="O7">
-        <v>0.44332526065800831</v>
+        <v>0.43444888148309457</v>
       </c>
       <c r="P7">
-        <v>0.48680765714354002</v>
+        <v>0.48067099853286799</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -978,49 +950,49 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>2.1660621371140661E-2</v>
+        <v>2.1072650907232929E-2</v>
       </c>
       <c r="C8">
-        <v>3.1588788461035078E-2</v>
+        <v>3.1864221585219177E-2</v>
       </c>
       <c r="D8">
-        <v>4.9237798388877763E-2</v>
+        <v>4.9510138867209903E-2</v>
       </c>
       <c r="E8">
-        <v>6.140293649020645E-2</v>
+        <v>6.3329394879119039E-2</v>
       </c>
       <c r="F8">
-        <v>6.567032416588392E-2</v>
+        <v>6.532319741103243E-2</v>
       </c>
       <c r="G8">
-        <v>0.10253826207334921</v>
+        <v>9.8295901096482785E-2</v>
       </c>
       <c r="H8">
-        <v>0.1104661343640725</v>
+        <v>0.1082705710235216</v>
       </c>
       <c r="I8">
-        <v>0.1513207431124752</v>
+        <v>0.1523700339255766</v>
       </c>
       <c r="J8">
-        <v>0.2086407572694359</v>
+        <v>0.2091429576646742</v>
       </c>
       <c r="K8">
-        <v>0.24200797143042391</v>
+        <v>0.2463853558066619</v>
       </c>
       <c r="L8">
-        <v>0.2759930577448183</v>
+        <v>0.28130297654545261</v>
       </c>
       <c r="M8">
-        <v>0.32771362641718749</v>
+        <v>0.33044015115705122</v>
       </c>
       <c r="N8">
-        <v>0.40446075405744158</v>
+        <v>0.40652335877239199</v>
       </c>
       <c r="O8">
-        <v>0.47315879944506462</v>
+        <v>0.47194720254655609</v>
       </c>
       <c r="P8">
-        <v>0.51873728138214736</v>
+        <v>0.51965555613832581</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1028,49 +1000,49 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>1.9835379780671292E-2</v>
+        <v>2.1181931343521029E-2</v>
       </c>
       <c r="C9">
-        <v>3.0407341514539828E-2</v>
+        <v>3.1350091268217313E-2</v>
       </c>
       <c r="D9">
-        <v>4.7975781311978771E-2</v>
+        <v>4.9953878871857323E-2</v>
       </c>
       <c r="E9">
-        <v>6.0557639041951772E-2</v>
+        <v>6.3003924956396284E-2</v>
       </c>
       <c r="F9">
-        <v>5.8891488888485499E-2</v>
+        <v>6.2308991641670697E-2</v>
       </c>
       <c r="G9">
-        <v>8.6635951479952178E-2</v>
+        <v>9.2314257265513011E-2</v>
       </c>
       <c r="H9">
-        <v>8.9242919173399216E-2</v>
+        <v>9.5904699541734972E-2</v>
       </c>
       <c r="I9">
-        <v>0.1040486740608934</v>
+        <v>0.1108003725503941</v>
       </c>
       <c r="J9">
-        <v>0.12772718263877131</v>
+        <v>0.1366506470581953</v>
       </c>
       <c r="K9">
-        <v>0.14932257088582121</v>
+        <v>0.1536043104535342</v>
       </c>
       <c r="L9">
-        <v>0.15442288747820121</v>
+        <v>0.15863772894850031</v>
       </c>
       <c r="M9">
-        <v>0.16921404539089749</v>
+        <v>0.17421269132833311</v>
       </c>
       <c r="N9">
-        <v>0.20474602554246521</v>
+        <v>0.21002475496595921</v>
       </c>
       <c r="O9">
-        <v>0.22778257510770761</v>
+        <v>0.2330651399145873</v>
       </c>
       <c r="P9">
-        <v>0.25023262079505898</v>
+        <v>0.25660297333795778</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1078,49 +1050,49 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>2.24172743669247E-2</v>
+        <v>2.062063233158079E-2</v>
       </c>
       <c r="C10">
-        <v>3.2347303775702392E-2</v>
+        <v>3.057178264154237E-2</v>
       </c>
       <c r="D10">
-        <v>4.9072479602384922E-2</v>
+        <v>4.8642155834438087E-2</v>
       </c>
       <c r="E10">
-        <v>6.0846212211074557E-2</v>
+        <v>6.0599361034468828E-2</v>
       </c>
       <c r="F10">
-        <v>6.1736394385829452E-2</v>
+        <v>5.7712341635888231E-2</v>
       </c>
       <c r="G10">
-        <v>8.8643960224095153E-2</v>
+        <v>8.7716217644705941E-2</v>
       </c>
       <c r="H10">
-        <v>9.0758463796058342E-2</v>
+        <v>9.0607164044868571E-2</v>
       </c>
       <c r="I10">
-        <v>0.1045296139693148</v>
+        <v>0.1045385215969898</v>
       </c>
       <c r="J10">
-        <v>0.1272271760941999</v>
+        <v>0.12509421289260569</v>
       </c>
       <c r="K10">
-        <v>0.14486287360840139</v>
+        <v>0.144587421471147</v>
       </c>
       <c r="L10">
-        <v>0.1494552268200863</v>
+        <v>0.15045463679209309</v>
       </c>
       <c r="M10">
-        <v>0.16478536429400761</v>
+        <v>0.16606749717273209</v>
       </c>
       <c r="N10">
-        <v>0.19906218515416191</v>
+        <v>0.20118366278388239</v>
       </c>
       <c r="O10">
-        <v>0.2240238878067867</v>
+        <v>0.22660753077514381</v>
       </c>
       <c r="P10">
-        <v>0.2505270290778473</v>
+        <v>0.25620787734699041</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1128,49 +1100,49 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>2.1450450370443411E-2</v>
+        <v>2.1951430147225059E-2</v>
       </c>
       <c r="C11">
-        <v>3.136142416229859E-2</v>
+        <v>3.2459531480824033E-2</v>
       </c>
       <c r="D11">
-        <v>4.9869894231728162E-2</v>
+        <v>4.9287165552567513E-2</v>
       </c>
       <c r="E11">
-        <v>6.2859791430711964E-2</v>
+        <v>6.2930930540775032E-2</v>
       </c>
       <c r="F11">
-        <v>6.3127435422091205E-2</v>
+        <v>6.2528385426635524E-2</v>
       </c>
       <c r="G11">
-        <v>9.2337967855543934E-2</v>
+        <v>9.0804912331615362E-2</v>
       </c>
       <c r="H11">
-        <v>9.6588006647109759E-2</v>
+        <v>9.675618833472388E-2</v>
       </c>
       <c r="I11">
-        <v>0.11263252220013741</v>
+        <v>0.1148368253561927</v>
       </c>
       <c r="J11">
-        <v>0.13591858923109321</v>
+        <v>0.13915419966081061</v>
       </c>
       <c r="K11">
-        <v>0.1463451940299775</v>
+        <v>0.1503877733736538</v>
       </c>
       <c r="L11">
-        <v>0.14822658164957961</v>
+        <v>0.15099674992664791</v>
       </c>
       <c r="M11">
-        <v>0.16025349246112669</v>
+        <v>0.1655757564518697</v>
       </c>
       <c r="N11">
-        <v>0.19547203725536119</v>
+        <v>0.2000532494380188</v>
       </c>
       <c r="O11">
-        <v>0.226079430571302</v>
+        <v>0.22937127429128021</v>
       </c>
       <c r="P11">
-        <v>0.24568688456642621</v>
+        <v>0.24928797352360771</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1178,49 +1150,49 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>1.9638606811585909E-2</v>
+        <v>1.9886270231527451E-2</v>
       </c>
       <c r="C12">
-        <v>4.7384558604008593E-2</v>
+        <v>4.7320576755145671E-2</v>
       </c>
       <c r="D12">
-        <v>5.7650715832830102E-2</v>
+        <v>5.9229070815535412E-2</v>
       </c>
       <c r="E12">
-        <v>8.8833582920761933E-2</v>
+        <v>9.172046763083308E-2</v>
       </c>
       <c r="F12">
-        <v>0.10883850204240531</v>
+        <v>0.1089095574607382</v>
       </c>
       <c r="G12">
-        <v>0.1207597018787019</v>
+        <v>0.12186720697255039</v>
       </c>
       <c r="H12">
-        <v>0.15070670730202779</v>
+        <v>0.1522299281231955</v>
       </c>
       <c r="I12">
-        <v>0.20447704443130049</v>
+        <v>0.20536548425833689</v>
       </c>
       <c r="J12">
-        <v>0.28354849241348579</v>
+        <v>0.28349510197565819</v>
       </c>
       <c r="K12">
-        <v>0.35591998472501668</v>
+        <v>0.35517028019174812</v>
       </c>
       <c r="L12">
-        <v>0.44693215071301018</v>
+        <v>0.44583052582603178</v>
       </c>
       <c r="M12">
-        <v>0.48452514686591908</v>
+        <v>0.48624359282918411</v>
       </c>
       <c r="N12">
-        <v>0.49021805272181362</v>
+        <v>0.4933208270905694</v>
       </c>
       <c r="O12">
-        <v>0.49887017277856099</v>
+        <v>0.50332308718331842</v>
       </c>
       <c r="P12">
-        <v>0.53331097066534705</v>
+        <v>0.53810073386585677</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1228,49 +1200,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>2.2239212006480491E-2</v>
+        <v>2.157302144314233E-2</v>
       </c>
       <c r="C13">
-        <v>7.3006991788120978E-2</v>
+        <v>7.2535382251234015E-2</v>
       </c>
       <c r="D13">
-        <v>9.0943498007420853E-2</v>
+        <v>9.492336881681096E-2</v>
       </c>
       <c r="E13">
-        <v>9.9293627399726359E-2</v>
+        <v>0.1016809304464535</v>
       </c>
       <c r="F13">
-        <v>0.15359754224198829</v>
+        <v>0.15816391647133701</v>
       </c>
       <c r="G13">
-        <v>0.19327603520518569</v>
+        <v>0.19833977533018651</v>
       </c>
       <c r="H13">
-        <v>0.20975547364067099</v>
+        <v>0.2153572987887741</v>
       </c>
       <c r="I13">
-        <v>0.24448354558226529</v>
+        <v>0.24455163174791331</v>
       </c>
       <c r="J13">
-        <v>0.3369510775306484</v>
+        <v>0.3352108367637297</v>
       </c>
       <c r="K13">
-        <v>0.42225558762509252</v>
+        <v>0.42136133787121061</v>
       </c>
       <c r="L13">
-        <v>0.45386763275443381</v>
+        <v>0.45214350912006018</v>
       </c>
       <c r="M13">
-        <v>0.46763033367576778</v>
+        <v>0.46783751088609782</v>
       </c>
       <c r="N13">
-        <v>0.49799799829231112</v>
+        <v>0.49751562628635659</v>
       </c>
       <c r="O13">
-        <v>0.52041317982406898</v>
+        <v>0.51521531120370256</v>
       </c>
       <c r="P13">
-        <v>0.5624855390984993</v>
+        <v>0.55670717280485982</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1278,49 +1250,49 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>2.097779363153918E-2</v>
+        <v>2.1502186462465659E-2</v>
       </c>
       <c r="C14">
-        <v>3.1329134843861128E-2</v>
+        <v>3.1957144592313913E-2</v>
       </c>
       <c r="D14">
-        <v>4.7076441217167808E-2</v>
+        <v>4.6456370902206778E-2</v>
       </c>
       <c r="E14">
-        <v>5.0032937940546751E-2</v>
+        <v>4.8240178688382818E-2</v>
       </c>
       <c r="F14">
-        <v>7.5649102092628873E-2</v>
+        <v>7.2477881237540953E-2</v>
       </c>
       <c r="G14">
-        <v>6.7570382668931339E-2</v>
+        <v>7.1843944103380686E-2</v>
       </c>
       <c r="H14">
-        <v>9.0713378585286386E-2</v>
+        <v>9.2043823726098539E-2</v>
       </c>
       <c r="I14">
-        <v>0.1010974825898425</v>
+        <v>0.1032282135240479</v>
       </c>
       <c r="J14">
-        <v>0.1160406646732302</v>
+        <v>0.1184052380334405</v>
       </c>
       <c r="K14">
-        <v>0.13606581391695541</v>
+        <v>0.13949732497182449</v>
       </c>
       <c r="L14">
-        <v>0.14731236219559751</v>
+        <v>0.151609628157335</v>
       </c>
       <c r="M14">
-        <v>0.1717951854872016</v>
+        <v>0.17487651376244789</v>
       </c>
       <c r="N14">
-        <v>0.20386608900788381</v>
+        <v>0.20560323340678749</v>
       </c>
       <c r="O14">
-        <v>0.2436421192265272</v>
+        <v>0.24985204560038021</v>
       </c>
       <c r="P14">
-        <v>0.29445035011590021</v>
+        <v>0.29987795794055178</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1328,49 +1300,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>2.3211582368510671E-2</v>
+        <v>2.245666694736537E-2</v>
       </c>
       <c r="C15">
-        <v>3.44724514806245E-2</v>
+        <v>3.1789614399374777E-2</v>
       </c>
       <c r="D15">
-        <v>5.0282491805908713E-2</v>
+        <v>4.6306388891186323E-2</v>
       </c>
       <c r="E15">
-        <v>5.1870221749504952E-2</v>
+        <v>4.9284407243878281E-2</v>
       </c>
       <c r="F15">
-        <v>7.8597855821632034E-2</v>
+        <v>7.4049636115356754E-2</v>
       </c>
       <c r="G15">
-        <v>7.012259329068582E-2</v>
+        <v>6.7493554463448402E-2</v>
       </c>
       <c r="H15">
-        <v>9.5678275385905898E-2</v>
+        <v>8.9195816958907548E-2</v>
       </c>
       <c r="I15">
-        <v>0.1039454710746293</v>
+        <v>9.9023307905270586E-2</v>
       </c>
       <c r="J15">
-        <v>0.116158931511784</v>
+        <v>0.1137299850448559</v>
       </c>
       <c r="K15">
-        <v>0.1374638140866847</v>
+        <v>0.13256540552750151</v>
       </c>
       <c r="L15">
-        <v>0.1490298544728775</v>
+        <v>0.1427959166257875</v>
       </c>
       <c r="M15">
-        <v>0.17313016515012419</v>
+        <v>0.1693388443197659</v>
       </c>
       <c r="N15">
-        <v>0.21274882475782819</v>
+        <v>0.20685246712567679</v>
       </c>
       <c r="O15">
-        <v>0.24241395988803879</v>
+        <v>0.23504535956332229</v>
       </c>
       <c r="P15">
-        <v>0.25690316215666498</v>
+        <v>0.25426284190339909</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1378,49 +1350,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>2.23462251956375E-2</v>
+        <v>2.1173583981748841E-2</v>
       </c>
       <c r="C16">
-        <v>3.2582972871359812E-2</v>
+        <v>3.1179652637343461E-2</v>
       </c>
       <c r="D16">
-        <v>4.9734376247661423E-2</v>
+        <v>4.7421566732663067E-2</v>
       </c>
       <c r="E16">
-        <v>5.213815409709277E-2</v>
+        <v>5.0242914974435227E-2</v>
       </c>
       <c r="F16">
-        <v>7.8423172536140506E-2</v>
+        <v>7.5925331524761441E-2</v>
       </c>
       <c r="G16">
-        <v>7.2128370278699339E-2</v>
+        <v>7.0151386815485828E-2</v>
       </c>
       <c r="H16">
-        <v>9.3558452347297649E-2</v>
+        <v>9.1119494023703229E-2</v>
       </c>
       <c r="I16">
-        <v>0.10362982106981131</v>
+        <v>9.9650859046713114E-2</v>
       </c>
       <c r="J16">
-        <v>0.11745725989674111</v>
+        <v>0.11197298150727911</v>
       </c>
       <c r="K16">
-        <v>0.13830529313133799</v>
+        <v>0.13113859450219501</v>
       </c>
       <c r="L16">
-        <v>0.1459083206349818</v>
+        <v>0.14184263038784661</v>
       </c>
       <c r="M16">
-        <v>0.1797337053936372</v>
+        <v>0.17659438429230451</v>
       </c>
       <c r="N16">
-        <v>0.2226908536847034</v>
+        <v>0.2216207664845212</v>
       </c>
       <c r="O16">
-        <v>0.25689349227766017</v>
+        <v>0.25555333564081972</v>
       </c>
       <c r="P16">
-        <v>0.2657447340807344</v>
+        <v>0.26751754782836218</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1428,49 +1400,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>2.1537742006329848E-2</v>
+        <v>2.2369352992719031E-2</v>
       </c>
       <c r="C17">
-        <v>3.1356758687674291E-2</v>
+        <v>3.3144155592735418E-2</v>
       </c>
       <c r="D17">
-        <v>4.6024769659665073E-2</v>
+        <v>5.010902293690267E-2</v>
       </c>
       <c r="E17">
-        <v>4.8747435649009067E-2</v>
+        <v>5.3393357781594257E-2</v>
       </c>
       <c r="F17">
-        <v>7.373221023838572E-2</v>
-      </c>
-      <c r="G17" s="2">
-        <v>6.7232475896018218E-2</v>
+        <v>7.9283523144220047E-2</v>
+      </c>
+      <c r="G17">
+        <v>7.1968577398212608E-2</v>
       </c>
       <c r="H17">
-        <v>8.8642215120865342E-2</v>
+        <v>9.4001072168497291E-2</v>
       </c>
       <c r="I17">
-        <v>9.7889285064475584E-2</v>
+        <v>0.1020205724689882</v>
       </c>
       <c r="J17">
-        <v>0.11024488472457659</v>
+        <v>0.11314097556498311</v>
       </c>
       <c r="K17">
-        <v>0.13126203182593141</v>
+        <v>0.1329182398327137</v>
       </c>
       <c r="L17">
-        <v>0.13846298281400729</v>
+        <v>0.1387502692569792</v>
       </c>
       <c r="M17">
-        <v>0.17758240116987811</v>
+        <v>0.17676619437012889</v>
       </c>
       <c r="N17">
-        <v>0.21800239170635671</v>
+        <v>0.21616925331274039</v>
       </c>
       <c r="O17">
-        <v>0.25426742871211161</v>
+        <v>0.2520406724855202</v>
       </c>
       <c r="P17">
-        <v>0.2657872321407676</v>
+        <v>0.26281216247890421</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1478,49 +1450,49 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>1.977860924601094E-2</v>
+        <v>2.0539739106764762E-2</v>
       </c>
       <c r="C18">
-        <v>4.9944109502610523E-2</v>
+        <v>4.7921128123660117E-2</v>
       </c>
       <c r="D18">
-        <v>6.1387549438371103E-2</v>
+        <v>6.3347741798996382E-2</v>
       </c>
       <c r="E18">
-        <v>9.8269947496877452E-2</v>
+        <v>0.10199789541294681</v>
       </c>
       <c r="F18">
-        <v>0.10965591504414531</v>
+        <v>0.11076392385733561</v>
       </c>
       <c r="G18">
-        <v>0.13672745385052321</v>
+        <v>0.1400734500050497</v>
       </c>
       <c r="H18">
-        <v>0.15399759932922241</v>
+        <v>0.15632525077181161</v>
       </c>
       <c r="I18">
-        <v>0.20693655336107261</v>
+        <v>0.2051712470405512</v>
       </c>
       <c r="J18">
-        <v>0.28015819405772507</v>
+        <v>0.27815208229152127</v>
       </c>
       <c r="K18">
-        <v>0.35876940805295948</v>
+        <v>0.35385047104701778</v>
       </c>
       <c r="L18">
-        <v>0.43612732473437471</v>
+        <v>0.42922287773808859</v>
       </c>
       <c r="M18">
-        <v>0.47502078210129378</v>
+        <v>0.46835730281529231</v>
       </c>
       <c r="N18">
-        <v>0.48858835203733619</v>
+        <v>0.4841861005622265</v>
       </c>
       <c r="O18">
-        <v>0.49583297176901331</v>
+        <v>0.49032053758888872</v>
       </c>
       <c r="P18">
-        <v>0.50330917970638933</v>
+        <v>0.49754983717471479</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1528,49 +1500,49 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>2.0654626848438221E-2</v>
+        <v>1.9384239379676371E-2</v>
       </c>
       <c r="C19">
-        <v>4.5107805663658913E-2</v>
+        <v>4.4244852790760847E-2</v>
       </c>
       <c r="D19">
-        <v>5.5925565154458123E-2</v>
+        <v>5.5500064198107817E-2</v>
       </c>
       <c r="E19">
-        <v>8.7123099184494679E-2</v>
+        <v>8.4141226379288447E-2</v>
       </c>
       <c r="F19">
-        <v>8.4806990944832683E-2</v>
+        <v>8.4096075495863176E-2</v>
       </c>
       <c r="G19">
-        <v>0.1249551165413865</v>
+        <v>0.12374483605363321</v>
       </c>
       <c r="H19">
-        <v>0.12927762834649989</v>
+        <v>0.12879853227469751</v>
       </c>
       <c r="I19">
-        <v>0.17094914368033301</v>
+        <v>0.1669737252159661</v>
       </c>
       <c r="J19">
-        <v>0.21846610265206631</v>
+        <v>0.21433046456609131</v>
       </c>
       <c r="K19">
-        <v>0.26866907935242129</v>
+        <v>0.26591236503537902</v>
       </c>
       <c r="L19">
-        <v>0.32113725593860409</v>
+        <v>0.31813067788810601</v>
       </c>
       <c r="M19">
-        <v>0.35946179445856269</v>
+        <v>0.35647370635375419</v>
       </c>
       <c r="N19">
-        <v>0.40428328442387418</v>
+        <v>0.40224354113771771</v>
       </c>
       <c r="O19">
-        <v>0.43251052935055317</v>
+        <v>0.4287213505425182</v>
       </c>
       <c r="P19">
-        <v>0.46546932472443642</v>
+        <v>0.46034018404360411</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1578,49 +1550,49 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>1.860637233401952E-2</v>
+        <v>1.9131054504578748E-2</v>
       </c>
       <c r="C20">
-        <v>3.7658876721205381E-2</v>
+        <v>3.6489462134885242E-2</v>
       </c>
       <c r="D20">
-        <v>5.4760429361843888E-2</v>
+        <v>5.2734801623036787E-2</v>
       </c>
       <c r="E20">
-        <v>8.5568564585249862E-2</v>
+        <v>8.1278513478414749E-2</v>
       </c>
       <c r="F20">
-        <v>7.9630846509724629E-2</v>
+        <v>7.6958589437227554E-2</v>
       </c>
       <c r="G20">
-        <v>8.8570445364422157E-2</v>
+        <v>8.5758589840205901E-2</v>
       </c>
       <c r="H20">
-        <v>0.111658153614259</v>
+        <v>0.106160467913576</v>
       </c>
       <c r="I20">
-        <v>0.15808552243562729</v>
+        <v>0.1521747483091116</v>
       </c>
       <c r="J20">
-        <v>0.18890302603153919</v>
+        <v>0.18450188199923859</v>
       </c>
       <c r="K20">
-        <v>0.21239034162253939</v>
+        <v>0.2105457385007414</v>
       </c>
       <c r="L20">
-        <v>0.25644055071066402</v>
+        <v>0.24887722880253521</v>
       </c>
       <c r="M20">
-        <v>0.29195046415287818</v>
+        <v>0.28578967348227552</v>
       </c>
       <c r="N20">
-        <v>0.30437506517817547</v>
+        <v>0.29978983176917978</v>
       </c>
       <c r="O20">
-        <v>0.34138662620127258</v>
+        <v>0.338398922834729</v>
       </c>
       <c r="P20">
-        <v>0.37927310223063632</v>
+        <v>0.37930897126623092</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1628,49 +1600,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>3.9256127019260463E-2</v>
+        <v>3.7700900232258083E-2</v>
       </c>
       <c r="C21">
-        <v>3.7178954027764062E-2</v>
+        <v>3.6220223496544857E-2</v>
       </c>
       <c r="D21">
-        <v>6.4951788570386859E-2</v>
+        <v>6.4947460524535927E-2</v>
       </c>
       <c r="E21">
-        <v>0.15917225743509611</v>
+        <v>0.16052813074907971</v>
       </c>
       <c r="F21">
-        <v>0.13767537741411071</v>
+        <v>0.1380570795802829</v>
       </c>
       <c r="G21">
-        <v>0.16489795602772411</v>
+        <v>0.1609841203637348</v>
       </c>
       <c r="H21">
-        <v>0.24580391727721909</v>
+        <v>0.24560562692952981</v>
       </c>
       <c r="I21">
-        <v>0.34537922300915952</v>
+        <v>0.3348810100193656</v>
       </c>
       <c r="J21">
-        <v>0.38176366862720579</v>
+        <v>0.37422050833915721</v>
       </c>
       <c r="K21">
-        <v>0.43995320549824579</v>
+        <v>0.43187800486138261</v>
       </c>
       <c r="L21">
-        <v>0.4726074186157222</v>
+        <v>0.4656185728582522</v>
       </c>
       <c r="M21">
-        <v>0.49796441464633517</v>
+        <v>0.49380984843366421</v>
       </c>
       <c r="N21">
-        <v>0.51959059001295993</v>
+        <v>0.51420838755453335</v>
       </c>
       <c r="O21">
-        <v>0.52506148366400429</v>
+        <v>0.51855378178525502</v>
       </c>
       <c r="P21">
-        <v>0.55586546434542095</v>
+        <v>0.54710996575912541</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1678,49 +1650,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>4.1347572667376431E-2</v>
+        <v>3.941483044482913E-2</v>
       </c>
       <c r="C22">
-        <v>3.9932485172391119E-2</v>
+        <v>3.7241382625481163E-2</v>
       </c>
       <c r="D22">
-        <v>6.6121490090403356E-2</v>
+        <v>6.2634150400258659E-2</v>
       </c>
       <c r="E22">
-        <v>0.16393684378631099</v>
+        <v>0.16155371807864011</v>
       </c>
       <c r="F22">
-        <v>0.14353225679616069</v>
+        <v>0.1431356805035883</v>
       </c>
       <c r="G22">
-        <v>0.15646448441011901</v>
+        <v>0.15279867095745939</v>
       </c>
       <c r="H22">
-        <v>0.25487134671249018</v>
+        <v>0.24881335452063519</v>
       </c>
       <c r="I22">
-        <v>0.33658630248128218</v>
+        <v>0.3262512275458922</v>
       </c>
       <c r="J22">
-        <v>0.39588312833106998</v>
+        <v>0.38527053313664428</v>
       </c>
       <c r="K22">
-        <v>0.43900526936879691</v>
+        <v>0.42369134654932689</v>
       </c>
       <c r="L22">
-        <v>0.48481008827065453</v>
+        <v>0.46751904473757738</v>
       </c>
       <c r="M22">
-        <v>0.51766146282548853</v>
+        <v>0.49952557857594421</v>
       </c>
       <c r="N22">
-        <v>0.51642359983837105</v>
+        <v>0.4984998583934947</v>
       </c>
       <c r="O22">
-        <v>0.52200822215606957</v>
+        <v>0.50147365112219244</v>
       </c>
       <c r="P22">
-        <v>0.56430917356377019</v>
+        <v>0.5478640862368952</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1728,49 +1700,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>2.0978688200220419E-2</v>
+        <v>2.1810678655214358E-2</v>
       </c>
       <c r="C23">
-        <v>3.456629254936916E-2</v>
+        <v>3.376030359660076E-2</v>
       </c>
       <c r="D23">
-        <v>9.1421050203808196E-2</v>
+        <v>9.0697528348000711E-2</v>
       </c>
       <c r="E23">
-        <v>7.1862627704245119E-2</v>
+        <v>7.3671027603425254E-2</v>
       </c>
       <c r="F23">
-        <v>0.16066368194161851</v>
+        <v>0.16057762848110829</v>
       </c>
       <c r="G23">
-        <v>0.25645617584034219</v>
+        <v>0.2464753537917371</v>
       </c>
       <c r="H23">
-        <v>0.34758908330053051</v>
+        <v>0.34222050582717112</v>
       </c>
       <c r="I23">
-        <v>0.38684431918945428</v>
+        <v>0.3806337738121171</v>
       </c>
       <c r="J23">
-        <v>0.40240788164311958</v>
+        <v>0.3947458265394736</v>
       </c>
       <c r="K23">
-        <v>0.46828714446919112</v>
+        <v>0.4629749017574572</v>
       </c>
       <c r="L23">
-        <v>0.51691289674191765</v>
+        <v>0.51253872434441416</v>
       </c>
       <c r="M23">
-        <v>0.55669331216139006</v>
+        <v>0.54819080559960276</v>
       </c>
       <c r="N23">
-        <v>0.59921706714766565</v>
+        <v>0.59097070455852463</v>
       </c>
       <c r="O23">
-        <v>0.61603757483990951</v>
+        <v>0.61090427466139274</v>
       </c>
       <c r="P23">
-        <v>0.65666715649893037</v>
+        <v>0.65260158011510683</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1778,49 +1750,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>4.762596506879796E-2</v>
+        <v>4.5836375610687742E-2</v>
       </c>
       <c r="C24">
-        <v>0.11643117746762879</v>
+        <v>0.1168985208912261</v>
       </c>
       <c r="D24">
-        <v>0.12305402204190211</v>
+        <v>0.12657278247417331</v>
       </c>
       <c r="E24">
-        <v>0.17665573781697541</v>
+        <v>0.17630606109313929</v>
       </c>
       <c r="F24">
-        <v>0.39685909528757768</v>
+        <v>0.39084731800591449</v>
       </c>
       <c r="G24">
-        <v>0.42887579341815418</v>
+        <v>0.42218057152787319</v>
       </c>
       <c r="H24">
-        <v>0.54422636956889914</v>
+        <v>0.53038815146898832</v>
       </c>
       <c r="I24">
-        <v>0.70441387412565837</v>
+        <v>0.68201393547197586</v>
       </c>
       <c r="J24">
-        <v>0.86890679026995021</v>
+        <v>0.85038517531585633</v>
       </c>
       <c r="K24">
-        <v>1.034351791146747</v>
+        <v>1.005660970035205</v>
       </c>
       <c r="L24">
-        <v>1.082790570375108</v>
+        <v>1.059083430600724</v>
       </c>
       <c r="M24">
-        <v>1.10437908684201</v>
+        <v>1.091542484143772</v>
       </c>
       <c r="N24">
-        <v>1.1151736319343231</v>
+        <v>1.086776276214203</v>
       </c>
       <c r="O24">
-        <v>1.114180660119392</v>
+        <v>1.0817145668842201</v>
       </c>
       <c r="P24">
-        <v>1.1385819309021501</v>
+        <v>1.104796395030945</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1828,49 +1800,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>7.3334159706722357E-2</v>
+        <v>6.9342673346376324E-2</v>
       </c>
       <c r="C25">
-        <v>0.14315640157670639</v>
+        <v>0.13335761195815141</v>
       </c>
       <c r="D25">
-        <v>0.1907643965392336</v>
+        <v>0.1789363259355731</v>
       </c>
       <c r="E25">
-        <v>0.27688097289557401</v>
+        <v>0.27045733539875888</v>
       </c>
       <c r="F25">
-        <v>0.35795829903420212</v>
+        <v>0.35277525778308888</v>
       </c>
       <c r="G25">
-        <v>0.51464357281845519</v>
+        <v>0.50478883549451437</v>
       </c>
       <c r="H25">
-        <v>0.67435361407060457</v>
+        <v>0.66911543800176354</v>
       </c>
       <c r="I25">
-        <v>0.84746622770203595</v>
+        <v>0.83024670742669948</v>
       </c>
       <c r="J25">
-        <v>1.049395995793988</v>
+        <v>1.029582190861827</v>
       </c>
       <c r="K25">
-        <v>1.20764708844574</v>
+        <v>1.190304932731381</v>
       </c>
       <c r="L25">
-        <v>1.3737527064201469</v>
+        <v>1.3675941906642699</v>
       </c>
       <c r="M25">
-        <v>1.5429221334004519</v>
+        <v>1.551509854092916</v>
       </c>
       <c r="N25">
-        <v>1.653278025547479</v>
+        <v>1.6594298673034129</v>
       </c>
       <c r="O25">
-        <v>1.7687639062627729</v>
+        <v>1.772940793871892</v>
       </c>
       <c r="P25">
-        <v>1.8353179492732929</v>
+        <v>1.845752328202851</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1878,49 +1850,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>4.4177773848167137E-2</v>
+        <v>4.2019761527461133E-2</v>
       </c>
       <c r="C26">
-        <v>9.1517260011534068E-2</v>
+        <v>8.6679511341316906E-2</v>
       </c>
       <c r="D26">
-        <v>9.4290959185932138E-2</v>
+        <v>8.9352686180260571E-2</v>
       </c>
       <c r="E26">
-        <v>0.1191960536024616</v>
+        <v>0.1163346654249017</v>
       </c>
       <c r="F26">
-        <v>0.18273432993077901</v>
+        <v>0.18442728830972871</v>
       </c>
       <c r="G26">
-        <v>0.24000904206460619</v>
+        <v>0.24875404648562</v>
       </c>
       <c r="H26">
-        <v>0.3273797005190261</v>
+        <v>0.32941911882929559</v>
       </c>
       <c r="I26">
-        <v>0.34371053746278102</v>
+        <v>0.35205863889770123</v>
       </c>
       <c r="J26">
-        <v>0.40061326989700752</v>
+        <v>0.39982669030773937</v>
       </c>
       <c r="K26">
-        <v>0.43214011396918378</v>
+        <v>0.43744117661034038</v>
       </c>
       <c r="L26">
-        <v>0.51271615397188586</v>
+        <v>0.505401415022525</v>
       </c>
       <c r="M26">
-        <v>0.55638760876817439</v>
+        <v>0.56486986407271322</v>
       </c>
       <c r="N26">
-        <v>0.66569540559462104</v>
+        <v>0.67434655692510226</v>
       </c>
       <c r="O26">
-        <v>0.68782161039273648</v>
+        <v>0.695154706700577</v>
       </c>
       <c r="P26">
-        <v>0.75194917716543264</v>
+        <v>0.76405849724141428</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1928,49 +1900,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>4.5041920691605439E-2</v>
+        <v>4.7641644709575742E-2</v>
       </c>
       <c r="C27">
-        <v>7.4925767166820312E-2</v>
+        <v>7.9049525013338964E-2</v>
       </c>
       <c r="D27">
-        <v>0.17121863417476099</v>
+        <v>0.1703272322283598</v>
       </c>
       <c r="E27">
-        <v>0.13275619619484449</v>
+        <v>0.13569243105373641</v>
       </c>
       <c r="F27">
-        <v>0.2115863732723321</v>
+        <v>0.21353782670254801</v>
       </c>
       <c r="G27">
-        <v>0.32425745115492732</v>
+        <v>0.33051783471576951</v>
       </c>
       <c r="H27">
-        <v>0.39490616430408848</v>
+        <v>0.40377558046275169</v>
       </c>
       <c r="I27">
-        <v>0.49386602765229443</v>
+        <v>0.50451191967014997</v>
       </c>
       <c r="J27">
-        <v>0.54255036771750054</v>
+        <v>0.55453565648987935</v>
       </c>
       <c r="K27">
-        <v>0.5772138358387422</v>
+        <v>0.58273297994211493</v>
       </c>
       <c r="L27">
-        <v>0.60972519470043507</v>
+        <v>0.61487243108994016</v>
       </c>
       <c r="M27">
-        <v>0.72323492635131414</v>
+        <v>0.72528880923035821</v>
       </c>
       <c r="N27">
-        <v>0.79712707464974131</v>
+        <v>0.79869142865729503</v>
       </c>
       <c r="O27">
-        <v>0.92742962911875793</v>
+        <v>0.92419432464279494</v>
       </c>
       <c r="P27">
-        <v>1.035991177743339</v>
+        <v>1.027354330519235</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1978,49 +1950,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>2.0124167015684199E-2</v>
+        <v>2.0100157926440598E-2</v>
       </c>
       <c r="C28">
-        <v>3.122692391129922E-2</v>
+        <v>3.1404784861044921E-2</v>
       </c>
       <c r="D28">
-        <v>7.6231868478690457E-2</v>
+        <v>7.5591987626138502E-2</v>
       </c>
       <c r="E28">
-        <v>6.2098481823695588E-2</v>
+        <v>6.3432939272812794E-2</v>
       </c>
       <c r="F28">
-        <v>7.6612587305209146E-2</v>
+        <v>7.7443488835566843E-2</v>
       </c>
       <c r="G28">
-        <v>8.6991023343968688E-2</v>
+        <v>8.8968791013139259E-2</v>
       </c>
       <c r="H28">
-        <v>0.1138240742207179</v>
+        <v>0.11639034892552449</v>
       </c>
       <c r="I28">
-        <v>0.18848166598400401</v>
+        <v>0.19161631032303089</v>
       </c>
       <c r="J28">
-        <v>0.21392156164634299</v>
+        <v>0.21810029796854871</v>
       </c>
       <c r="K28">
-        <v>0.24943391402946341</v>
+        <v>0.2513751435286069</v>
       </c>
       <c r="L28">
-        <v>0.29916970656631381</v>
+        <v>0.29772577978976922</v>
       </c>
       <c r="M28">
-        <v>0.37602550110111937</v>
+        <v>0.37427072776626491</v>
       </c>
       <c r="N28">
-        <v>0.42155473655149578</v>
+        <v>0.41820017247674368</v>
       </c>
       <c r="O28">
-        <v>0.4951701556039918</v>
+        <v>0.48979975970288753</v>
       </c>
       <c r="P28">
-        <v>0.56750674533563239</v>
+        <v>0.56106225185081671</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2028,49 +2000,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>2.1013410777608991E-2</v>
+        <v>1.938705469320379E-2</v>
       </c>
       <c r="C29">
-        <v>3.2167274648374322E-2</v>
+        <v>3.0857835988044039E-2</v>
       </c>
       <c r="D29">
-        <v>8.0546580316315675E-2</v>
+        <v>7.9147374598806275E-2</v>
       </c>
       <c r="E29">
-        <v>6.7590384916549229E-2</v>
+        <v>6.552893335739407E-2</v>
       </c>
       <c r="F29">
-        <v>8.8814746442078985E-2</v>
+        <v>8.5753997367645551E-2</v>
       </c>
       <c r="G29">
-        <v>0.13264933297223461</v>
+        <v>0.12673407616645449</v>
       </c>
       <c r="H29">
-        <v>0.17106515698633851</v>
+        <v>0.16535319032218301</v>
       </c>
       <c r="I29">
-        <v>0.21854956094495059</v>
+        <v>0.2112972466184154</v>
       </c>
       <c r="J29">
-        <v>0.23502504421499609</v>
+        <v>0.23306854103974711</v>
       </c>
       <c r="K29">
-        <v>0.2507542479192526</v>
+        <v>0.25110671697813353</v>
       </c>
       <c r="L29">
-        <v>0.28730536159970649</v>
+        <v>0.29375685850668842</v>
       </c>
       <c r="M29">
-        <v>0.34500818913977599</v>
+        <v>0.35420084661975509</v>
       </c>
       <c r="N29">
-        <v>0.41570381503793691</v>
+        <v>0.42497156275452352</v>
       </c>
       <c r="O29">
-        <v>0.45786846807659592</v>
+        <v>0.47283340636863802</v>
       </c>
       <c r="P29">
-        <v>0.53674008670625351</v>
+        <v>0.55404395915277127</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2078,49 +2050,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>1.829392224933268E-2</v>
+        <v>1.8425218216366779E-2</v>
       </c>
       <c r="C30">
-        <v>3.0881290561428631E-2</v>
+        <v>3.0872422251360439E-2</v>
       </c>
       <c r="D30">
-        <v>7.2319131842504381E-2</v>
+        <v>7.1784902461499711E-2</v>
       </c>
       <c r="E30">
-        <v>6.8067594986281121E-2</v>
+        <v>6.8212134131020785E-2</v>
       </c>
       <c r="F30">
-        <v>8.1927032592989057E-2</v>
+        <v>8.0506999716136618E-2</v>
       </c>
       <c r="G30">
-        <v>8.8781419847447141E-2</v>
+        <v>9.10758846100862E-2</v>
       </c>
       <c r="H30">
-        <v>0.1276936586852524</v>
+        <v>0.12750681013619489</v>
       </c>
       <c r="I30">
-        <v>0.19407563512531351</v>
+        <v>0.19989314432967981</v>
       </c>
       <c r="J30">
-        <v>0.23683377169575309</v>
+        <v>0.2397495320449374</v>
       </c>
       <c r="K30">
-        <v>0.26907397258012528</v>
+        <v>0.27326094599907369</v>
       </c>
       <c r="L30">
-        <v>0.33193977513978551</v>
+        <v>0.33539218377852298</v>
       </c>
       <c r="M30">
-        <v>0.3892480074654151</v>
+        <v>0.39535727081645372</v>
       </c>
       <c r="N30">
-        <v>0.45819513988142191</v>
+        <v>0.46736143943194519</v>
       </c>
       <c r="O30">
-        <v>0.52215378290851988</v>
+        <v>0.53273576004986856</v>
       </c>
       <c r="P30">
-        <v>0.63737416463924357</v>
+        <v>0.6474873021319707</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2128,49 +2100,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>1.9386226419065958E-2</v>
+        <v>1.773734347406164E-2</v>
       </c>
       <c r="C31">
-        <v>3.2222831474093223E-2</v>
+        <v>3.0395525386558431E-2</v>
       </c>
       <c r="D31">
-        <v>7.2558297913504544E-2</v>
+        <v>7.0638893589399898E-2</v>
       </c>
       <c r="E31">
-        <v>6.9508203947329705E-2</v>
+        <v>6.6268737739753059E-2</v>
       </c>
       <c r="F31">
-        <v>7.9646479597030861E-2</v>
+        <v>7.7624518198343817E-2</v>
       </c>
       <c r="G31">
-        <v>8.3301543848695925E-2</v>
+        <v>7.9413532617861882E-2</v>
       </c>
       <c r="H31">
-        <v>9.7078651759043733E-2</v>
+        <v>9.3916417708891919E-2</v>
       </c>
       <c r="I31">
-        <v>0.13031241780511349</v>
+        <v>0.1231644767893175</v>
       </c>
       <c r="J31">
-        <v>0.14136724807504611</v>
+        <v>0.13717515905345079</v>
       </c>
       <c r="K31">
-        <v>0.14544462513178491</v>
+        <v>0.1414126455523648</v>
       </c>
       <c r="L31">
-        <v>0.15666106419143391</v>
+        <v>0.15349614936736139</v>
       </c>
       <c r="M31">
-        <v>0.1870000646789246</v>
+        <v>0.18631769103574891</v>
       </c>
       <c r="N31">
-        <v>0.23164034823267529</v>
+        <v>0.23187710734620839</v>
       </c>
       <c r="O31">
-        <v>0.23922827335901309</v>
+        <v>0.23784575100474939</v>
       </c>
       <c r="P31">
-        <v>0.3268357206131236</v>
+        <v>0.32791632731639642</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2178,49 +2150,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>2.0036817867055579E-2</v>
+        <v>2.06139692856665E-2</v>
       </c>
       <c r="C32">
-        <v>3.2000341138309192E-2</v>
+        <v>3.2006422211794061E-2</v>
       </c>
       <c r="D32">
-        <v>8.1216775402988328E-2</v>
+        <v>8.0574205377066277E-2</v>
       </c>
       <c r="E32">
-        <v>6.8605807710805711E-2</v>
+        <v>6.6090413187850361E-2</v>
       </c>
       <c r="F32">
-        <v>8.5008766329595864E-2</v>
+        <v>8.26879622148875E-2</v>
       </c>
       <c r="G32">
-        <v>0.1113390244966064</v>
+        <v>0.1074936117905312</v>
       </c>
       <c r="H32">
-        <v>0.13609972771340331</v>
+        <v>0.1308037102849515</v>
       </c>
       <c r="I32">
-        <v>0.14911400400936281</v>
+        <v>0.14076054545558339</v>
       </c>
       <c r="J32">
-        <v>0.1504256207209661</v>
+        <v>0.14530477388600341</v>
       </c>
       <c r="K32">
-        <v>0.151315286126704</v>
+        <v>0.1479833371026289</v>
       </c>
       <c r="L32">
-        <v>0.1614970544710416</v>
+        <v>0.16105789065927351</v>
       </c>
       <c r="M32">
-        <v>0.18296916778627231</v>
+        <v>0.18089858094034339</v>
       </c>
       <c r="N32">
-        <v>0.22233245433875731</v>
+        <v>0.2213453775542423</v>
       </c>
       <c r="O32">
-        <v>0.23672218989673471</v>
+        <v>0.23732656395772919</v>
       </c>
       <c r="P32">
-        <v>0.28789912541886858</v>
+        <v>0.28908842022928721</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2228,49 +2200,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>2.0227814366946321E-2</v>
+        <v>2.114149251389907E-2</v>
       </c>
       <c r="C33">
-        <v>3.1715480937739238E-2</v>
+        <v>3.0989896883784399E-2</v>
       </c>
       <c r="D33">
-        <v>7.7884421682764771E-2</v>
+        <v>7.8276414834348107E-2</v>
       </c>
       <c r="E33">
-        <v>6.4767802649970729E-2</v>
+        <v>6.6613610995768124E-2</v>
       </c>
       <c r="F33">
-        <v>8.0573077814260152E-2</v>
+        <v>8.360702095526551E-2</v>
       </c>
       <c r="G33">
-        <v>0.1044723464881516</v>
+        <v>0.110549357111474</v>
       </c>
       <c r="H33">
-        <v>0.12505285296897689</v>
+        <v>0.13095634952970031</v>
       </c>
       <c r="I33">
-        <v>0.14443101492277019</v>
+        <v>0.14704437780900931</v>
       </c>
       <c r="J33">
-        <v>0.14775204726762969</v>
+        <v>0.15204052768348661</v>
       </c>
       <c r="K33">
-        <v>0.14452956671667441</v>
+        <v>0.14800144992194</v>
       </c>
       <c r="L33">
-        <v>0.1553564926080564</v>
+        <v>0.1564073617101652</v>
       </c>
       <c r="M33">
-        <v>0.17521226706892151</v>
+        <v>0.17530403471530939</v>
       </c>
       <c r="N33">
-        <v>0.21290344573551021</v>
+        <v>0.2117645664164248</v>
       </c>
       <c r="O33">
-        <v>0.21895354297662889</v>
+        <v>0.22138922664129251</v>
       </c>
       <c r="P33">
-        <v>0.26865194383230251</v>
+        <v>0.26858885885927819</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2278,49 +2250,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>2.132465736960654E-2</v>
+        <v>2.181345896328701E-2</v>
       </c>
       <c r="C34">
-        <v>3.2876185410648628E-2</v>
+        <v>3.3433721113053871E-2</v>
       </c>
       <c r="D34">
-        <v>8.030912868017992E-2</v>
+        <v>8.2257271557590883E-2</v>
       </c>
       <c r="E34">
-        <v>6.8318324278790254E-2</v>
+        <v>7.1412682840639841E-2</v>
       </c>
       <c r="F34">
-        <v>8.5686089643523866E-2</v>
+        <v>8.7814557428353535E-2</v>
       </c>
       <c r="G34">
-        <v>0.1103696830430644</v>
+        <v>0.11334607282747081</v>
       </c>
       <c r="H34">
-        <v>0.12852472878935511</v>
+        <v>0.1337593199277971</v>
       </c>
       <c r="I34">
-        <v>0.1382187513901719</v>
+        <v>0.14691641767334571</v>
       </c>
       <c r="J34">
-        <v>0.1438674109525844</v>
+        <v>0.14878787997537629</v>
       </c>
       <c r="K34">
-        <v>0.14621880148143421</v>
+        <v>0.14972345213214039</v>
       </c>
       <c r="L34">
-        <v>0.1548589080273208</v>
+        <v>0.15689350181345679</v>
       </c>
       <c r="M34">
-        <v>0.17102983416841511</v>
+        <v>0.17611881122968021</v>
       </c>
       <c r="N34">
-        <v>0.19945010586182871</v>
+        <v>0.2067640029009834</v>
       </c>
       <c r="O34">
-        <v>0.2112705718552218</v>
+        <v>0.2155245730530205</v>
       </c>
       <c r="P34">
-        <v>0.25060662781852261</v>
+        <v>0.25585290468361571</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2328,49 +2300,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>1.9619757718437599E-2</v>
+        <v>2.085613914930684E-2</v>
       </c>
       <c r="C35">
-        <v>3.0298852877659651E-2</v>
+        <v>3.1203428963489929E-2</v>
       </c>
       <c r="D35">
-        <v>7.7257261972067393E-2</v>
+        <v>7.7576892042601209E-2</v>
       </c>
       <c r="E35">
-        <v>6.3203642442715258E-2</v>
+        <v>6.5838618582677366E-2</v>
       </c>
       <c r="F35">
-        <v>8.0126465750133713E-2</v>
+        <v>8.3528768646626617E-2</v>
       </c>
       <c r="G35">
-        <v>0.10243532367335099</v>
+        <v>0.1110132867447904</v>
       </c>
       <c r="H35">
-        <v>0.1206544639141391</v>
+        <v>0.13037401374457591</v>
       </c>
       <c r="I35">
-        <v>0.1325054481403154</v>
+        <v>0.14206412052810591</v>
       </c>
       <c r="J35">
-        <v>0.14325507748064761</v>
+        <v>0.14902358963825391</v>
       </c>
       <c r="K35">
-        <v>0.14142243648689129</v>
+        <v>0.14679579638860929</v>
       </c>
       <c r="L35">
-        <v>0.151456306221362</v>
+        <v>0.15626672441922521</v>
       </c>
       <c r="M35">
-        <v>0.1619472573256574</v>
+        <v>0.16704907346858239</v>
       </c>
       <c r="N35">
-        <v>0.1899324486293579</v>
+        <v>0.19410784074521559</v>
       </c>
       <c r="O35">
-        <v>0.196260848615879</v>
+        <v>0.2016389609484297</v>
       </c>
       <c r="P35">
-        <v>0.2249518116714477</v>
+        <v>0.23041191912868539</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2378,49 +2350,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>2.0050321451624002E-2</v>
+        <v>2.0813062718108791E-2</v>
       </c>
       <c r="C36">
-        <v>3.1158054862028831E-2</v>
+        <v>3.1606636482475192E-2</v>
       </c>
       <c r="D36">
-        <v>7.766563047155961E-2</v>
+        <v>7.8003624994584797E-2</v>
       </c>
       <c r="E36">
-        <v>6.7362319967877227E-2</v>
+        <v>6.5271856390368033E-2</v>
       </c>
       <c r="F36">
-        <v>8.2799268220585365E-2</v>
+        <v>8.2545457093948338E-2</v>
       </c>
       <c r="G36">
-        <v>0.1110481058790882</v>
+        <v>0.1081689117172082</v>
       </c>
       <c r="H36">
-        <v>0.1352014880583039</v>
+        <v>0.13219678067961241</v>
       </c>
       <c r="I36">
-        <v>0.1530626038431063</v>
+        <v>0.15273738735796549</v>
       </c>
       <c r="J36">
-        <v>0.15720468590809381</v>
+        <v>0.16153409273414299</v>
       </c>
       <c r="K36">
-        <v>0.15545251653318731</v>
+        <v>0.15690596715611929</v>
       </c>
       <c r="L36">
-        <v>0.17312918220975829</v>
+        <v>0.17138204397885551</v>
       </c>
       <c r="M36">
-        <v>0.20333401974116799</v>
+        <v>0.20326043650087181</v>
       </c>
       <c r="N36">
-        <v>0.25193053388280662</v>
+        <v>0.24947685194099711</v>
       </c>
       <c r="O36">
-        <v>0.25562778451886781</v>
+        <v>0.25178492480397491</v>
       </c>
       <c r="P36">
-        <v>0.29485589164734749</v>
+        <v>0.29595631089369989</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2428,49 +2400,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>1.9157902278927771E-2</v>
+        <v>2.017713175905567E-2</v>
       </c>
       <c r="C37">
-        <v>2.9831650736347411E-2</v>
+        <v>3.1231786124048529E-2</v>
       </c>
       <c r="D37">
-        <v>7.4296220738572671E-2</v>
+        <v>7.78980948070781E-2</v>
       </c>
       <c r="E37">
-        <v>6.3597202539511621E-2</v>
+        <v>6.5485698582931295E-2</v>
       </c>
       <c r="F37">
-        <v>8.1066547051175886E-2</v>
+        <v>8.2176302906483145E-2</v>
       </c>
       <c r="G37">
-        <v>0.10749915941376161</v>
+        <v>0.1091284298285745</v>
       </c>
       <c r="H37">
-        <v>0.13071651861545891</v>
+        <v>0.13165471966708239</v>
       </c>
       <c r="I37">
-        <v>0.14877046697602991</v>
+        <v>0.14911604621415531</v>
       </c>
       <c r="J37">
-        <v>0.15125677972155219</v>
+        <v>0.15437858571815899</v>
       </c>
       <c r="K37">
-        <v>0.14822446982959181</v>
+        <v>0.15179243963045369</v>
       </c>
       <c r="L37">
-        <v>0.16614396140557819</v>
+        <v>0.16899501032491709</v>
       </c>
       <c r="M37">
-        <v>0.1962915813912611</v>
+        <v>0.19500872124543511</v>
       </c>
       <c r="N37">
-        <v>0.23607105809790591</v>
+        <v>0.2364753171297834</v>
       </c>
       <c r="O37">
-        <v>0.2395686518388245</v>
+        <v>0.24093809796300361</v>
       </c>
       <c r="P37">
-        <v>0.27974365215225799</v>
+        <v>0.27757082643813069</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2478,49 +2450,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>1.9303142196563709E-2</v>
+        <v>2.0247274103130208E-2</v>
       </c>
       <c r="C38">
-        <v>3.0719912402576769E-2</v>
+        <v>3.1127916964105769E-2</v>
       </c>
       <c r="D38">
-        <v>7.9695918785157693E-2</v>
+        <v>7.6876685927370514E-2</v>
       </c>
       <c r="E38">
-        <v>6.7440134921247896E-2</v>
+        <v>6.5687360050236232E-2</v>
       </c>
       <c r="F38">
-        <v>8.4025257175212031E-2</v>
+        <v>8.3530626145346898E-2</v>
       </c>
       <c r="G38">
-        <v>0.10823709019092009</v>
+        <v>0.1116024201820514</v>
       </c>
       <c r="H38">
-        <v>0.13345362911945741</v>
+        <v>0.13365031026268739</v>
       </c>
       <c r="I38">
-        <v>0.14977797693935141</v>
+        <v>0.14941963262649599</v>
       </c>
       <c r="J38">
-        <v>0.15141641513293469</v>
+        <v>0.15155962223020769</v>
       </c>
       <c r="K38">
-        <v>0.15027712309611729</v>
+        <v>0.1465357637976771</v>
       </c>
       <c r="L38">
-        <v>0.16666086486051551</v>
+        <v>0.15823696635800019</v>
       </c>
       <c r="M38">
-        <v>0.1962553681395556</v>
+        <v>0.18504320823998369</v>
       </c>
       <c r="N38">
-        <v>0.23847106155353601</v>
+        <v>0.22708473718784389</v>
       </c>
       <c r="O38">
-        <v>0.2415393176789801</v>
+        <v>0.22722244077458079</v>
       </c>
       <c r="P38">
-        <v>0.2800914043855891</v>
+        <v>0.26506094209788272</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2528,49 +2500,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>2.0552001228767439E-2</v>
+        <v>2.0897314723638091E-2</v>
       </c>
       <c r="C39">
-        <v>3.2891236753720847E-2</v>
+        <v>3.196769342386041E-2</v>
       </c>
       <c r="D39">
-        <v>8.1555238967483734E-2</v>
+        <v>8.0008959907379662E-2</v>
       </c>
       <c r="E39">
-        <v>6.8939519151929307E-2</v>
+        <v>6.6984674859697724E-2</v>
       </c>
       <c r="F39">
-        <v>8.5312365455719186E-2</v>
+        <v>8.3872603047691396E-2</v>
       </c>
       <c r="G39">
-        <v>0.11076803404774969</v>
+        <v>0.11111509621605591</v>
       </c>
       <c r="H39">
-        <v>0.13450453968180109</v>
+        <v>0.1350249064264023</v>
       </c>
       <c r="I39">
-        <v>0.14803100430371149</v>
+        <v>0.15422628987453971</v>
       </c>
       <c r="J39">
-        <v>0.1518194420856441</v>
+        <v>0.15728769080620941</v>
       </c>
       <c r="K39">
-        <v>0.1467374141855512</v>
+        <v>0.14947281180042959</v>
       </c>
       <c r="L39">
-        <v>0.15822693283925229</v>
+        <v>0.1612813490129604</v>
       </c>
       <c r="M39">
-        <v>0.18147155726785219</v>
+        <v>0.19182953923090351</v>
       </c>
       <c r="N39">
-        <v>0.22188618140231109</v>
+        <v>0.22791841781974381</v>
       </c>
       <c r="O39">
-        <v>0.22209673550210199</v>
+        <v>0.23017179893061959</v>
       </c>
       <c r="P39">
-        <v>0.254272878644485</v>
+        <v>0.26198006296659132</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2578,49 +2550,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>1.808157821792267E-2</v>
+        <v>1.9176992815742588E-2</v>
       </c>
       <c r="C40">
-        <v>2.938838454534665E-2</v>
+        <v>3.1483098445273187E-2</v>
       </c>
       <c r="D40">
-        <v>7.3439188662103083E-2</v>
+        <v>8.2411206380285873E-2</v>
       </c>
       <c r="E40">
-        <v>6.2662637752407546E-2</v>
+        <v>6.8979147966873433E-2</v>
       </c>
       <c r="F40">
-        <v>7.8637146633388166E-2</v>
+        <v>8.5158101698448951E-2</v>
       </c>
       <c r="G40">
-        <v>0.1040963136255959</v>
+        <v>0.1093518699886398</v>
       </c>
       <c r="H40">
-        <v>0.12653684837935411</v>
+        <v>0.12914795508571769</v>
       </c>
       <c r="I40">
-        <v>0.1353278119827814</v>
+        <v>0.14100044345437421</v>
       </c>
       <c r="J40">
-        <v>0.14254700276409221</v>
+        <v>0.15038078882597511</v>
       </c>
       <c r="K40">
-        <v>0.14044632086690581</v>
+        <v>0.1475761248728453</v>
       </c>
       <c r="L40">
-        <v>0.153372724842572</v>
+        <v>0.15537903414569981</v>
       </c>
       <c r="M40">
-        <v>0.16601745677304319</v>
+        <v>0.17058814319930179</v>
       </c>
       <c r="N40">
-        <v>0.1938888650923152</v>
+        <v>0.19719666993193671</v>
       </c>
       <c r="O40">
-        <v>0.19952357271388099</v>
+        <v>0.203178748898765</v>
       </c>
       <c r="P40">
-        <v>0.2235843819025094</v>
+        <v>0.22453343930937431</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2628,49 +2600,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>1.8228498280870139E-2</v>
+        <v>1.8170306105706469E-2</v>
       </c>
       <c r="C41">
-        <v>4.1834803938401999E-2</v>
+        <v>4.1533614676496973E-2</v>
       </c>
       <c r="D41">
-        <v>8.3889466249799205E-2</v>
+        <v>8.2902188251708253E-2</v>
       </c>
       <c r="E41">
-        <v>0.1055443194952445</v>
+        <v>0.10493488951893951</v>
       </c>
       <c r="F41">
-        <v>0.16765969739356451</v>
+        <v>0.1660220121405025</v>
       </c>
       <c r="G41">
-        <v>0.23843312060110591</v>
+        <v>0.23689993942979809</v>
       </c>
       <c r="H41">
-        <v>0.24661646801926651</v>
+        <v>0.2461120983322532</v>
       </c>
       <c r="I41">
-        <v>0.26951554886949891</v>
+        <v>0.27196171957389448</v>
       </c>
       <c r="J41">
-        <v>0.29399471382233938</v>
+        <v>0.29906077577006768</v>
       </c>
       <c r="K41">
-        <v>0.34025995817445709</v>
+        <v>0.34349765045653607</v>
       </c>
       <c r="L41">
-        <v>0.39852833749635108</v>
+        <v>0.39819858933500668</v>
       </c>
       <c r="M41">
-        <v>0.46460284141195679</v>
+        <v>0.46631060780238448</v>
       </c>
       <c r="N41">
-        <v>0.56221210607327421</v>
+        <v>0.57003508263571678</v>
       </c>
       <c r="O41">
-        <v>0.6250024432495509</v>
+        <v>0.63420640167297404</v>
       </c>
       <c r="P41">
-        <v>0.68461389432266206</v>
+        <v>0.69902774433154413</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2678,49 +2650,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>1.8189972954064659E-2</v>
+        <v>1.7869540552223891E-2</v>
       </c>
       <c r="C42">
-        <v>3.779930547991972E-2</v>
+        <v>3.5436181428718183E-2</v>
       </c>
       <c r="D42">
-        <v>6.6273795223106835E-2</v>
+        <v>6.7618449847532625E-2</v>
       </c>
       <c r="E42">
-        <v>7.8172839949331996E-2</v>
+        <v>7.9514876326910566E-2</v>
       </c>
       <c r="F42">
-        <v>0.1041812952939847</v>
+        <v>0.1057995477930076</v>
       </c>
       <c r="G42">
-        <v>0.1349711360234109</v>
+        <v>0.1370231459131962</v>
       </c>
       <c r="H42">
-        <v>0.1530896080806238</v>
+        <v>0.15282482673445599</v>
       </c>
       <c r="I42">
-        <v>0.20574805958367609</v>
+        <v>0.20983947211848811</v>
       </c>
       <c r="J42">
-        <v>0.28121167231562788</v>
+        <v>0.28818365317723882</v>
       </c>
       <c r="K42">
-        <v>0.34236941886146077</v>
+        <v>0.35100796204038048</v>
       </c>
       <c r="L42">
-        <v>0.37263146945432329</v>
+        <v>0.38292421653767977</v>
       </c>
       <c r="M42">
-        <v>0.35391687282813439</v>
+        <v>0.3637430605767884</v>
       </c>
       <c r="N42">
-        <v>0.35271984526290701</v>
+        <v>0.36166148047003399</v>
       </c>
       <c r="O42">
-        <v>0.38304220246649828</v>
+        <v>0.39233091967314182</v>
       </c>
       <c r="P42">
-        <v>0.40692213747677441</v>
+        <v>0.41933472785458809</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2728,49 +2700,49 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>1.6002526364722661E-2</v>
+        <v>1.6463841993308859E-2</v>
       </c>
       <c r="C43">
-        <v>3.325684498740189E-2</v>
+        <v>3.3146401204700249E-2</v>
       </c>
       <c r="D43">
-        <v>5.9649861656878578E-2</v>
+        <v>6.1082949647376039E-2</v>
       </c>
       <c r="E43">
-        <v>7.3074212180884168E-2</v>
+        <v>7.4913402306769683E-2</v>
       </c>
       <c r="F43">
-        <v>9.6222684425403937E-2</v>
+        <v>0.1010253803736363</v>
       </c>
       <c r="G43">
-        <v>0.12404443250410691</v>
+        <v>0.12971441963723121</v>
       </c>
       <c r="H43">
-        <v>0.1242066157075344</v>
+        <v>0.12865866275156901</v>
       </c>
       <c r="I43">
-        <v>0.1587158127191314</v>
+        <v>0.16452962817145739</v>
       </c>
       <c r="J43">
-        <v>0.2410593067107043</v>
+        <v>0.25051046238487978</v>
       </c>
       <c r="K43">
-        <v>0.27912231896998208</v>
+        <v>0.29086354646559232</v>
       </c>
       <c r="L43">
-        <v>0.29935725043350481</v>
+        <v>0.31420109306034538</v>
       </c>
       <c r="M43">
-        <v>0.32538057717391028</v>
+        <v>0.33751731482856412</v>
       </c>
       <c r="N43">
-        <v>0.33818348997445069</v>
+        <v>0.34669957453235312</v>
       </c>
       <c r="O43">
-        <v>0.35194319598289142</v>
+        <v>0.35586708017893492</v>
       </c>
       <c r="P43">
-        <v>0.40302505341456102</v>
+        <v>0.41019790182589572</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -2778,49 +2750,49 @@
         <v>58</v>
       </c>
       <c r="B44">
-        <v>2.623529142821068E-2</v>
+        <v>2.647620488376146E-2</v>
       </c>
       <c r="C44">
-        <v>4.5941077987043499E-2</v>
+        <v>4.4889169908363891E-2</v>
       </c>
       <c r="D44">
-        <v>0.10569996738390371</v>
+        <v>0.1045943883100361</v>
       </c>
       <c r="E44">
-        <v>0.1063632603169615</v>
+        <v>0.1041805018649964</v>
       </c>
       <c r="F44">
-        <v>0.12656732312170549</v>
+        <v>0.12709492668885369</v>
       </c>
       <c r="G44">
-        <v>0.17255278714546099</v>
+        <v>0.17055660434448799</v>
       </c>
       <c r="H44">
-        <v>0.23499347759553041</v>
+        <v>0.23262635085030481</v>
       </c>
       <c r="I44">
-        <v>0.28993925367054191</v>
+        <v>0.28930821181617622</v>
       </c>
       <c r="J44">
-        <v>0.32703011337656562</v>
+        <v>0.32569626140271429</v>
       </c>
       <c r="K44">
-        <v>0.36111573760612992</v>
+        <v>0.35886081345172011</v>
       </c>
       <c r="L44">
-        <v>0.41687552098366748</v>
+        <v>0.41412180229952927</v>
       </c>
       <c r="M44">
-        <v>0.50245779192726281</v>
+        <v>0.50205398161310821</v>
       </c>
       <c r="N44">
-        <v>0.60876304939778414</v>
+        <v>0.61532783153173332</v>
       </c>
       <c r="O44">
-        <v>0.71630957786008498</v>
+        <v>0.71627307882266755</v>
       </c>
       <c r="P44">
-        <v>0.77353425402732634</v>
+        <v>0.77520745473832553</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -2828,49 +2800,49 @@
         <v>59</v>
       </c>
       <c r="B45">
-        <v>3.3270253722887277E-2</v>
+        <v>3.2693653896679553E-2</v>
       </c>
       <c r="C45">
-        <v>5.2541583238391983E-2</v>
+        <v>5.4133089074558827E-2</v>
       </c>
       <c r="D45">
-        <v>0.17014535659956551</v>
+        <v>0.1732426851492341</v>
       </c>
       <c r="E45">
-        <v>0.21438064763962661</v>
+        <v>0.21732487742838449</v>
       </c>
       <c r="F45">
-        <v>0.2370803690686302</v>
+        <v>0.23512767172505561</v>
       </c>
       <c r="G45">
-        <v>0.31237782809994669</v>
+        <v>0.30375821386200552</v>
       </c>
       <c r="H45">
-        <v>0.34507497783030378</v>
+        <v>0.33403263565233282</v>
       </c>
       <c r="I45">
-        <v>0.36519368525445561</v>
+        <v>0.35778456246881768</v>
       </c>
       <c r="J45">
-        <v>0.40752715686224678</v>
+        <v>0.40034983013132253</v>
       </c>
       <c r="K45">
-        <v>0.44636276120018031</v>
+        <v>0.43741702246906222</v>
       </c>
       <c r="L45">
-        <v>0.52044144237546197</v>
+        <v>0.509946418437772</v>
       </c>
       <c r="M45">
-        <v>0.63370225648148559</v>
+        <v>0.61985089043244579</v>
       </c>
       <c r="N45">
-        <v>0.68169106772965238</v>
+        <v>0.668573506761722</v>
       </c>
       <c r="O45">
-        <v>0.72879923226709087</v>
+        <v>0.72056283762118578</v>
       </c>
       <c r="P45">
-        <v>0.76732310891786626</v>
+        <v>0.75939442854593475</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -2878,49 +2850,49 @@
         <v>60</v>
       </c>
       <c r="B46">
-        <v>4.2052753511200358E-2</v>
+        <v>4.1201326161696139E-2</v>
       </c>
       <c r="C46">
-        <v>4.2785536244931532E-2</v>
+        <v>4.1928197436166381E-2</v>
       </c>
       <c r="D46">
-        <v>0.105850168557581</v>
+        <v>0.1037779692160431</v>
       </c>
       <c r="E46">
-        <v>0.20555497759234179</v>
+        <v>0.2042898596972289</v>
       </c>
       <c r="F46">
-        <v>0.21214307966852261</v>
+        <v>0.21457015083095199</v>
       </c>
       <c r="G46">
-        <v>0.20764794288354169</v>
+        <v>0.20782238307781301</v>
       </c>
       <c r="H46">
-        <v>0.24330200297518459</v>
+        <v>0.2429544585321487</v>
       </c>
       <c r="I46">
-        <v>0.31822986421615318</v>
+        <v>0.32075366229231389</v>
       </c>
       <c r="J46">
-        <v>0.42521703349754142</v>
+        <v>0.42087649501816121</v>
       </c>
       <c r="K46">
-        <v>0.49295400922442228</v>
+        <v>0.48812635532474358</v>
       </c>
       <c r="L46">
-        <v>0.55306113663447487</v>
+        <v>0.55063348623158648</v>
       </c>
       <c r="M46">
-        <v>0.60700207155697372</v>
+        <v>0.60165168692189397</v>
       </c>
       <c r="N46">
-        <v>0.64446168075926635</v>
+        <v>0.63391068940755224</v>
       </c>
       <c r="O46">
-        <v>0.70272298100042085</v>
+        <v>0.69015342500743748</v>
       </c>
       <c r="P46">
-        <v>0.76907369904564904</v>
+        <v>0.75099347484573808</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -2928,57 +2900,57 @@
         <v>61</v>
       </c>
       <c r="B47">
-        <v>2.2163505379733769E-2</v>
+        <v>2.3298799256052272E-2</v>
       </c>
       <c r="C47">
-        <v>6.9476635871254411E-2</v>
+        <v>7.2337671727419228E-2</v>
       </c>
       <c r="D47">
-        <v>0.11651199724033159</v>
+        <v>0.1188097031442039</v>
       </c>
       <c r="E47">
-        <v>0.13194247490915759</v>
+        <v>0.132767188474015</v>
       </c>
       <c r="F47">
-        <v>0.2055660301574227</v>
+        <v>0.2035605555555805</v>
       </c>
       <c r="G47">
-        <v>0.23437507256456441</v>
+        <v>0.23056754184333789</v>
       </c>
       <c r="H47">
-        <v>0.2814894608117573</v>
+        <v>0.27810712845922553</v>
       </c>
       <c r="I47">
-        <v>0.3147374803383779</v>
+        <v>0.31422013238856911</v>
       </c>
       <c r="J47">
-        <v>0.37488867449484953</v>
+        <v>0.37327304288477092</v>
       </c>
       <c r="K47">
-        <v>0.45783784701282182</v>
+        <v>0.45894027699178208</v>
       </c>
       <c r="L47">
-        <v>0.53897676013573093</v>
+        <v>0.53969961121071386</v>
       </c>
       <c r="M47">
-        <v>0.59948778925304924</v>
+        <v>0.59875507276087625</v>
       </c>
       <c r="N47">
-        <v>0.62769506837551625</v>
+        <v>0.62863888794634193</v>
       </c>
       <c r="O47">
-        <v>0.63969817618174485</v>
+        <v>0.64343676774002989</v>
       </c>
       <c r="P47">
-        <v>0.66469319032115415</v>
+        <v>0.66926984584770555</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P16 B18:P47 B17:F17 H17:P17">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X13.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -344,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -376,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -411,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -587,2373 +350,2277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>2.45213213053645E-2</v>
+        <v>0.02406972128985019</v>
       </c>
       <c r="C2">
-        <v>3.6009367228646887E-2</v>
+        <v>0.03426239021457855</v>
       </c>
       <c r="D2">
-        <v>4.4235671134611132E-2</v>
+        <v>0.04445603739042081</v>
       </c>
       <c r="E2">
-        <v>5.1703411367836183E-2</v>
+        <v>0.05342272425563743</v>
       </c>
       <c r="F2">
-        <v>9.6456364521967042E-2</v>
+        <v>0.09808964774124462</v>
       </c>
       <c r="G2">
-        <v>8.1015777899707597E-2</v>
+        <v>0.0835509555362115</v>
       </c>
       <c r="H2">
-        <v>9.532868542804751E-2</v>
+        <v>0.09896259100269533</v>
       </c>
       <c r="I2">
-        <v>0.1378374972320664</v>
+        <v>0.1395383528824401</v>
       </c>
       <c r="J2">
-        <v>0.12809607773988491</v>
+        <v>0.1343347262181672</v>
       </c>
       <c r="K2">
-        <v>0.15277521815634559</v>
+        <v>0.1598224672891664</v>
       </c>
       <c r="L2">
-        <v>0.18050541400866979</v>
+        <v>0.1864755544499948</v>
       </c>
       <c r="M2">
-        <v>0.22854696902232299</v>
+        <v>0.2392661665138228</v>
       </c>
       <c r="N2">
-        <v>0.31484120443508212</v>
+        <v>0.3238305742040932</v>
       </c>
       <c r="O2">
-        <v>0.37968198703154937</v>
+        <v>0.3958089667065677</v>
       </c>
       <c r="P2">
-        <v>0.42075244978898668</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4326417408982691</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>3.8577989308622107E-2</v>
+        <v>0.0388846288186861</v>
       </c>
       <c r="C3">
-        <v>3.7406487672083211E-2</v>
+        <v>0.03594244399979163</v>
       </c>
       <c r="D3">
-        <v>6.6182588410944376E-2</v>
+        <v>0.06488134317380045</v>
       </c>
       <c r="E3">
-        <v>0.1559745947009806</v>
+        <v>0.1579600492643117</v>
       </c>
       <c r="F3">
-        <v>0.13991770553698499</v>
+        <v>0.1404950385839135</v>
       </c>
       <c r="G3">
-        <v>0.1655356754552606</v>
+        <v>0.1692426840139705</v>
       </c>
       <c r="H3">
-        <v>0.23803987717491931</v>
+        <v>0.2368901706469027</v>
       </c>
       <c r="I3">
-        <v>0.26825646603021358</v>
+        <v>0.2714398011297819</v>
       </c>
       <c r="J3">
-        <v>0.33522299233580499</v>
+        <v>0.337965781686665</v>
       </c>
       <c r="K3">
-        <v>0.37155324443023202</v>
+        <v>0.3726480446080134</v>
       </c>
       <c r="L3">
-        <v>0.42019822091252867</v>
+        <v>0.4234366758773169</v>
       </c>
       <c r="M3">
-        <v>0.47622525791940851</v>
+        <v>0.4786576932975436</v>
       </c>
       <c r="N3">
-        <v>0.53460137062539714</v>
+        <v>0.5335883417339022</v>
       </c>
       <c r="O3">
-        <v>0.54680205133378557</v>
+        <v>0.5466065230314199</v>
       </c>
       <c r="P3">
-        <v>0.5427024272005625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.5400277007421661</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>2.258606246832684E-2</v>
+        <v>0.02198725168221061</v>
       </c>
       <c r="C4">
-        <v>3.362951467201436E-2</v>
+        <v>0.03316854925031909</v>
       </c>
       <c r="D4">
-        <v>4.4290826110612969E-2</v>
+        <v>0.04275905706128202</v>
       </c>
       <c r="E4">
-        <v>6.3443598343427166E-2</v>
+        <v>0.06084537731224282</v>
       </c>
       <c r="F4">
-        <v>9.5682028556264731E-2</v>
+        <v>0.09079041488296091</v>
       </c>
       <c r="G4">
-        <v>8.3113513888668278E-2</v>
+        <v>0.08295622735897934</v>
       </c>
       <c r="H4">
-        <v>9.3281673518419095E-2</v>
+        <v>0.09297182380011093</v>
       </c>
       <c r="I4">
-        <v>0.1198147676038975</v>
+        <v>0.1180087296309373</v>
       </c>
       <c r="J4">
-        <v>0.1637998153464395</v>
+        <v>0.1606593729886414</v>
       </c>
       <c r="K4">
-        <v>0.21676301846459911</v>
+        <v>0.2089456986583658</v>
       </c>
       <c r="L4">
-        <v>0.25925727193650833</v>
+        <v>0.2488809051105881</v>
       </c>
       <c r="M4">
-        <v>0.33936204764659172</v>
+        <v>0.3290330368604316</v>
       </c>
       <c r="N4">
-        <v>0.4044073407900699</v>
+        <v>0.3921627630312524</v>
       </c>
       <c r="O4">
-        <v>0.44939557874991881</v>
+        <v>0.4359953435539586</v>
       </c>
       <c r="P4">
-        <v>0.49307452792150391</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4848319505270974</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>2.154971411649154E-2</v>
+        <v>0.01950234127783956</v>
       </c>
       <c r="C5">
-        <v>5.0226310015631707E-2</v>
+        <v>0.04741195363891548</v>
       </c>
       <c r="D5">
-        <v>6.0966171994775047E-2</v>
+        <v>0.05907066622014279</v>
       </c>
       <c r="E5">
-        <v>0.10067236235072551</v>
+        <v>0.09695535262248411</v>
       </c>
       <c r="F5">
-        <v>0.1206391937768949</v>
+        <v>0.1164318029581017</v>
       </c>
       <c r="G5">
-        <v>0.13425290819344221</v>
+        <v>0.1301342591242648</v>
       </c>
       <c r="H5">
-        <v>0.15875881393545899</v>
+        <v>0.1554241169158169</v>
       </c>
       <c r="I5">
-        <v>0.21688514737115691</v>
+        <v>0.2164452196284936</v>
       </c>
       <c r="J5">
-        <v>0.31596415794511368</v>
+        <v>0.3136746984108985</v>
       </c>
       <c r="K5">
-        <v>0.37300665045240139</v>
+        <v>0.370666452592122</v>
       </c>
       <c r="L5">
-        <v>0.42906123203252139</v>
+        <v>0.4288372547211173</v>
       </c>
       <c r="M5">
-        <v>0.44978185353122158</v>
+        <v>0.4517149035017631</v>
       </c>
       <c r="N5">
-        <v>0.45977127766185172</v>
+        <v>0.4609272023427946</v>
       </c>
       <c r="O5">
-        <v>0.47247913197700558</v>
+        <v>0.4699514741428964</v>
       </c>
       <c r="P5">
-        <v>0.49018804175776198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.4832810677281704</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>2.001611139291137E-2</v>
+        <v>0.02059155683042346</v>
       </c>
       <c r="C6">
-        <v>4.5318774408722229E-2</v>
+        <v>0.04572563489711789</v>
       </c>
       <c r="D6">
-        <v>5.5947759705443523E-2</v>
+        <v>0.05706032984645237</v>
       </c>
       <c r="E6">
-        <v>8.9833955701822288E-2</v>
+        <v>0.09123833449097407</v>
       </c>
       <c r="F6">
-        <v>9.3720788154539325E-2</v>
+        <v>0.09564130908555879</v>
       </c>
       <c r="G6">
-        <v>0.1072149710378575</v>
+        <v>0.1082335672850303</v>
       </c>
       <c r="H6">
-        <v>0.1523916278641689</v>
+        <v>0.1541882768483999</v>
       </c>
       <c r="I6">
-        <v>0.19363626189759661</v>
+        <v>0.1967254774191847</v>
       </c>
       <c r="J6">
-        <v>0.24081463191027669</v>
+        <v>0.2415784620503366</v>
       </c>
       <c r="K6">
-        <v>0.26932788717933331</v>
+        <v>0.2714732226949074</v>
       </c>
       <c r="L6">
-        <v>0.31565464383126152</v>
+        <v>0.3205686517562806</v>
       </c>
       <c r="M6">
-        <v>0.35150000395472508</v>
+        <v>0.3570266476025046</v>
       </c>
       <c r="N6">
-        <v>0.39445883243448521</v>
+        <v>0.394726922382242</v>
       </c>
       <c r="O6">
-        <v>0.41205062676211829</v>
+        <v>0.4098764594844488</v>
       </c>
       <c r="P6">
-        <v>0.43387096346033027</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4357556404412128</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>2.1646419924492451E-2</v>
+        <v>0.02481144046563599</v>
       </c>
       <c r="C7">
-        <v>3.0698606256638561E-2</v>
+        <v>0.03223677318485185</v>
       </c>
       <c r="D7">
-        <v>4.6204315984067823E-2</v>
+        <v>0.04734018657056083</v>
       </c>
       <c r="E7">
-        <v>4.8822657980890923E-2</v>
+        <v>0.05076836151083119</v>
       </c>
       <c r="F7">
-        <v>7.5750469813129939E-2</v>
+        <v>0.07563573018825298</v>
       </c>
       <c r="G7">
-        <v>7.143300994472801E-2</v>
+        <v>0.07321578715502775</v>
       </c>
       <c r="H7">
-        <v>0.10229797223031491</v>
+        <v>0.09853501978991774</v>
       </c>
       <c r="I7">
-        <v>0.1181063114762408</v>
+        <v>0.1144640362054218</v>
       </c>
       <c r="J7">
-        <v>0.1468285585796992</v>
+        <v>0.1474389148888284</v>
       </c>
       <c r="K7">
-        <v>0.18593784098211119</v>
+        <v>0.1844828186869123</v>
       </c>
       <c r="L7">
-        <v>0.23438080366630301</v>
+        <v>0.2301401280329914</v>
       </c>
       <c r="M7">
-        <v>0.31861184121150871</v>
+        <v>0.3083019758713003</v>
       </c>
       <c r="N7">
-        <v>0.37347629054715348</v>
+        <v>0.364939712085687</v>
       </c>
       <c r="O7">
-        <v>0.43444888148309457</v>
+        <v>0.4277422630775481</v>
       </c>
       <c r="P7">
-        <v>0.48067099853286799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4667065766241868</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>2.1072650907232929E-2</v>
+        <v>0.02124766125200217</v>
       </c>
       <c r="C8">
-        <v>3.1864221585219177E-2</v>
+        <v>0.03140045511519918</v>
       </c>
       <c r="D8">
-        <v>4.9510138867209903E-2</v>
+        <v>0.04974637815669458</v>
       </c>
       <c r="E8">
-        <v>6.3329394879119039E-2</v>
+        <v>0.06510565304718807</v>
       </c>
       <c r="F8">
-        <v>6.532319741103243E-2</v>
+        <v>0.06624618214523903</v>
       </c>
       <c r="G8">
-        <v>9.8295901096482785E-2</v>
+        <v>0.1054287867503693</v>
       </c>
       <c r="H8">
-        <v>0.1082705710235216</v>
+        <v>0.1149101599161206</v>
       </c>
       <c r="I8">
-        <v>0.1523700339255766</v>
+        <v>0.1616046913590283</v>
       </c>
       <c r="J8">
-        <v>0.2091429576646742</v>
+        <v>0.2214257648931273</v>
       </c>
       <c r="K8">
-        <v>0.2463853558066619</v>
+        <v>0.259989506678036</v>
       </c>
       <c r="L8">
-        <v>0.28130297654545261</v>
+        <v>0.292219960582506</v>
       </c>
       <c r="M8">
-        <v>0.33044015115705122</v>
+        <v>0.343525218930351</v>
       </c>
       <c r="N8">
-        <v>0.40652335877239199</v>
+        <v>0.4207624179732662</v>
       </c>
       <c r="O8">
-        <v>0.47194720254655609</v>
+        <v>0.4870764056828214</v>
       </c>
       <c r="P8">
-        <v>0.51965555613832581</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.5321114739082707</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>2.1181931343521029E-2</v>
+        <v>0.02252751089146088</v>
       </c>
       <c r="C9">
-        <v>3.1350091268217313E-2</v>
+        <v>0.03383559462275876</v>
       </c>
       <c r="D9">
-        <v>4.9953878871857323E-2</v>
+        <v>0.05180280336842857</v>
       </c>
       <c r="E9">
-        <v>6.3003924956396284E-2</v>
+        <v>0.06436524193887294</v>
       </c>
       <c r="F9">
-        <v>6.2308991641670697E-2</v>
+        <v>0.0608850685120671</v>
       </c>
       <c r="G9">
-        <v>9.2314257265513011E-2</v>
+        <v>0.091444429538038</v>
       </c>
       <c r="H9">
-        <v>9.5904699541734972E-2</v>
+        <v>0.09499096651603656</v>
       </c>
       <c r="I9">
-        <v>0.1108003725503941</v>
+        <v>0.1104306162615259</v>
       </c>
       <c r="J9">
-        <v>0.1366506470581953</v>
+        <v>0.1365282890656305</v>
       </c>
       <c r="K9">
-        <v>0.1536043104535342</v>
+        <v>0.1582164133677532</v>
       </c>
       <c r="L9">
-        <v>0.15863772894850031</v>
+        <v>0.1634779596313589</v>
       </c>
       <c r="M9">
-        <v>0.17421269132833311</v>
+        <v>0.1810140247855561</v>
       </c>
       <c r="N9">
-        <v>0.21002475496595921</v>
+        <v>0.215897555556153</v>
       </c>
       <c r="O9">
-        <v>0.2330651399145873</v>
+        <v>0.2407205966048332</v>
       </c>
       <c r="P9">
-        <v>0.25660297333795778</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.2631507060664566</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>2.062063233158079E-2</v>
+        <v>0.02037917607847517</v>
       </c>
       <c r="C10">
-        <v>3.057178264154237E-2</v>
+        <v>0.03208607395179675</v>
       </c>
       <c r="D10">
-        <v>4.8642155834438087E-2</v>
+        <v>0.05055635400633218</v>
       </c>
       <c r="E10">
-        <v>6.0599361034468828E-2</v>
+        <v>0.06307028861378439</v>
       </c>
       <c r="F10">
-        <v>5.7712341635888231E-2</v>
+        <v>0.06190235548748035</v>
       </c>
       <c r="G10">
-        <v>8.7716217644705941E-2</v>
+        <v>0.09229130815535824</v>
       </c>
       <c r="H10">
-        <v>9.0607164044868571E-2</v>
+        <v>0.0948080009998995</v>
       </c>
       <c r="I10">
-        <v>0.1045385215969898</v>
+        <v>0.108960881250343</v>
       </c>
       <c r="J10">
-        <v>0.12509421289260569</v>
+        <v>0.1324312972389058</v>
       </c>
       <c r="K10">
-        <v>0.144587421471147</v>
+        <v>0.1522127924034269</v>
       </c>
       <c r="L10">
-        <v>0.15045463679209309</v>
+        <v>0.1566748533909316</v>
       </c>
       <c r="M10">
-        <v>0.16606749717273209</v>
+        <v>0.1727336947539083</v>
       </c>
       <c r="N10">
-        <v>0.20118366278388239</v>
+        <v>0.2083218813489481</v>
       </c>
       <c r="O10">
-        <v>0.22660753077514381</v>
+        <v>0.2361785388726247</v>
       </c>
       <c r="P10">
-        <v>0.25620787734699041</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.2649315215093484</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>2.1951430147225059E-2</v>
+        <v>0.02083835388968475</v>
       </c>
       <c r="C11">
-        <v>3.2459531480824033E-2</v>
+        <v>0.02984116531261205</v>
       </c>
       <c r="D11">
-        <v>4.9287165552567513E-2</v>
+        <v>0.04804882615383654</v>
       </c>
       <c r="E11">
-        <v>6.2930930540775032E-2</v>
+        <v>0.06215283469566935</v>
       </c>
       <c r="F11">
-        <v>6.2528385426635524E-2</v>
+        <v>0.06026820963395052</v>
       </c>
       <c r="G11">
-        <v>9.0804912331615362E-2</v>
+        <v>0.09011303876099008</v>
       </c>
       <c r="H11">
-        <v>9.675618833472388E-2</v>
+        <v>0.09488276036053978</v>
       </c>
       <c r="I11">
-        <v>0.1148368253561927</v>
+        <v>0.1097223769017921</v>
       </c>
       <c r="J11">
-        <v>0.13915419966081061</v>
+        <v>0.133899795820557</v>
       </c>
       <c r="K11">
-        <v>0.1503877733736538</v>
+        <v>0.1457411098415865</v>
       </c>
       <c r="L11">
-        <v>0.15099674992664791</v>
+        <v>0.1494116722309554</v>
       </c>
       <c r="M11">
-        <v>0.1655757564518697</v>
+        <v>0.1624463007614336</v>
       </c>
       <c r="N11">
-        <v>0.2000532494380188</v>
+        <v>0.1959573890837714</v>
       </c>
       <c r="O11">
-        <v>0.22937127429128021</v>
+        <v>0.225166078595058</v>
       </c>
       <c r="P11">
-        <v>0.24928797352360771</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.2428368903794165</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>1.9886270231527451E-2</v>
+        <v>0.02056848975755066</v>
       </c>
       <c r="C12">
-        <v>4.7320576755145671E-2</v>
+        <v>0.04789589014749251</v>
       </c>
       <c r="D12">
-        <v>5.9229070815535412E-2</v>
+        <v>0.05898843778477691</v>
       </c>
       <c r="E12">
-        <v>9.172046763083308E-2</v>
+        <v>0.09102421864911747</v>
       </c>
       <c r="F12">
-        <v>0.1089095574607382</v>
+        <v>0.1100651095689416</v>
       </c>
       <c r="G12">
-        <v>0.12186720697255039</v>
+        <v>0.1210638513315895</v>
       </c>
       <c r="H12">
-        <v>0.1522299281231955</v>
+        <v>0.1513570298021881</v>
       </c>
       <c r="I12">
-        <v>0.20536548425833689</v>
+        <v>0.204456019950376</v>
       </c>
       <c r="J12">
-        <v>0.28349510197565819</v>
+        <v>0.2848092959940216</v>
       </c>
       <c r="K12">
-        <v>0.35517028019174812</v>
+        <v>0.3609318238269962</v>
       </c>
       <c r="L12">
-        <v>0.44583052582603178</v>
+        <v>0.4549337091802102</v>
       </c>
       <c r="M12">
-        <v>0.48624359282918411</v>
+        <v>0.494963341056022</v>
       </c>
       <c r="N12">
-        <v>0.4933208270905694</v>
+        <v>0.5003429505213456</v>
       </c>
       <c r="O12">
-        <v>0.50332308718331842</v>
+        <v>0.5053844275823094</v>
       </c>
       <c r="P12">
-        <v>0.53810073386585677</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.5403970374579325</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>2.157302144314233E-2</v>
+        <v>0.02182457012504513</v>
       </c>
       <c r="C13">
-        <v>7.2535382251234015E-2</v>
+        <v>0.07407771192074064</v>
       </c>
       <c r="D13">
-        <v>9.492336881681096E-2</v>
+        <v>0.09419335950455565</v>
       </c>
       <c r="E13">
-        <v>0.1016809304464535</v>
+        <v>0.104495326929208</v>
       </c>
       <c r="F13">
-        <v>0.15816391647133701</v>
+        <v>0.156612057030279</v>
       </c>
       <c r="G13">
-        <v>0.19833977533018651</v>
+        <v>0.2008718298621476</v>
       </c>
       <c r="H13">
-        <v>0.2153572987887741</v>
+        <v>0.2154651702427262</v>
       </c>
       <c r="I13">
-        <v>0.24455163174791331</v>
+        <v>0.244037026746233</v>
       </c>
       <c r="J13">
-        <v>0.3352108367637297</v>
+        <v>0.3358196897659236</v>
       </c>
       <c r="K13">
-        <v>0.42136133787121061</v>
+        <v>0.4198825948587486</v>
       </c>
       <c r="L13">
-        <v>0.45214350912006018</v>
+        <v>0.452559906544265</v>
       </c>
       <c r="M13">
-        <v>0.46783751088609782</v>
+        <v>0.4629984427426453</v>
       </c>
       <c r="N13">
-        <v>0.49751562628635659</v>
+        <v>0.4935003746019808</v>
       </c>
       <c r="O13">
-        <v>0.51521531120370256</v>
+        <v>0.5076053403371614</v>
       </c>
       <c r="P13">
-        <v>0.55670717280485982</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5486725153140166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>2.1502186462465659E-2</v>
+        <v>0.02255313958519811</v>
       </c>
       <c r="C14">
-        <v>3.1957144592313913E-2</v>
+        <v>0.0331192089370852</v>
       </c>
       <c r="D14">
-        <v>4.6456370902206778E-2</v>
+        <v>0.04972202596117192</v>
       </c>
       <c r="E14">
-        <v>4.8240178688382818E-2</v>
+        <v>0.05156720060674236</v>
       </c>
       <c r="F14">
-        <v>7.2477881237540953E-2</v>
+        <v>0.07566463767094767</v>
       </c>
       <c r="G14">
-        <v>7.1843944103380686E-2</v>
+        <v>0.06745675837010867</v>
       </c>
       <c r="H14">
-        <v>9.2043823726098539E-2</v>
+        <v>0.09260372333621958</v>
       </c>
       <c r="I14">
-        <v>0.1032282135240479</v>
+        <v>0.1031539849810476</v>
       </c>
       <c r="J14">
-        <v>0.1184052380334405</v>
+        <v>0.119177021140319</v>
       </c>
       <c r="K14">
-        <v>0.13949732497182449</v>
+        <v>0.1404969045687094</v>
       </c>
       <c r="L14">
-        <v>0.151609628157335</v>
+        <v>0.1517606197033634</v>
       </c>
       <c r="M14">
-        <v>0.17487651376244789</v>
+        <v>0.1807116031639849</v>
       </c>
       <c r="N14">
-        <v>0.20560323340678749</v>
+        <v>0.2137723142366406</v>
       </c>
       <c r="O14">
-        <v>0.24985204560038021</v>
+        <v>0.2563792967770936</v>
       </c>
       <c r="P14">
-        <v>0.29987795794055178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3109788051327859</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>2.245666694736537E-2</v>
+        <v>0.02192941115942398</v>
       </c>
       <c r="C15">
-        <v>3.1789614399374777E-2</v>
+        <v>0.03131438277385445</v>
       </c>
       <c r="D15">
-        <v>4.6306388891186323E-2</v>
+        <v>0.04811687616414573</v>
       </c>
       <c r="E15">
-        <v>4.9284407243878281E-2</v>
+        <v>0.05147181128014533</v>
       </c>
       <c r="F15">
-        <v>7.4049636115356754E-2</v>
+        <v>0.07485352710985615</v>
       </c>
       <c r="G15">
-        <v>6.7493554463448402E-2</v>
+        <v>0.07272118478992273</v>
       </c>
       <c r="H15">
-        <v>8.9195816958907548E-2</v>
+        <v>0.09188877240111304</v>
       </c>
       <c r="I15">
-        <v>9.9023307905270586E-2</v>
+        <v>0.1006453754174371</v>
       </c>
       <c r="J15">
-        <v>0.1137299850448559</v>
+        <v>0.1096139354383322</v>
       </c>
       <c r="K15">
-        <v>0.13256540552750151</v>
+        <v>0.1316852792500491</v>
       </c>
       <c r="L15">
-        <v>0.1427959166257875</v>
+        <v>0.1425976119373111</v>
       </c>
       <c r="M15">
-        <v>0.1693388443197659</v>
+        <v>0.1690894413678199</v>
       </c>
       <c r="N15">
-        <v>0.20685246712567679</v>
+        <v>0.2088134125904483</v>
       </c>
       <c r="O15">
-        <v>0.23504535956332229</v>
+        <v>0.2353644143015134</v>
       </c>
       <c r="P15">
-        <v>0.25426284190339909</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.2524579857081722</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>2.1173583981748841E-2</v>
+        <v>0.02016030016084502</v>
       </c>
       <c r="C16">
-        <v>3.1179652637343461E-2</v>
+        <v>0.03068303748520373</v>
       </c>
       <c r="D16">
-        <v>4.7421566732663067E-2</v>
+        <v>0.04585069522164931</v>
       </c>
       <c r="E16">
-        <v>5.0242914974435227E-2</v>
+        <v>0.04864491299533069</v>
       </c>
       <c r="F16">
-        <v>7.5925331524761441E-2</v>
+        <v>0.07257912795549115</v>
       </c>
       <c r="G16">
-        <v>7.0151386815485828E-2</v>
+        <v>0.06628071765272781</v>
       </c>
       <c r="H16">
-        <v>9.1119494023703229E-2</v>
+        <v>0.08937479127769021</v>
       </c>
       <c r="I16">
-        <v>9.9650859046713114E-2</v>
+        <v>0.09993433813851205</v>
       </c>
       <c r="J16">
-        <v>0.11197298150727911</v>
+        <v>0.1136779902745433</v>
       </c>
       <c r="K16">
-        <v>0.13113859450219501</v>
+        <v>0.1330572413232672</v>
       </c>
       <c r="L16">
-        <v>0.14184263038784661</v>
+        <v>0.1425333464844549</v>
       </c>
       <c r="M16">
-        <v>0.17659438429230451</v>
+        <v>0.178918570816934</v>
       </c>
       <c r="N16">
-        <v>0.2216207664845212</v>
+        <v>0.2247282141419613</v>
       </c>
       <c r="O16">
-        <v>0.25555333564081972</v>
+        <v>0.2598250187401329</v>
       </c>
       <c r="P16">
-        <v>0.26751754782836218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.2736611961256227</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>2.2369352992719031E-2</v>
+        <v>0.02297430417299418</v>
       </c>
       <c r="C17">
-        <v>3.3144155592735418E-2</v>
+        <v>0.03202498055010849</v>
       </c>
       <c r="D17">
-        <v>5.010902293690267E-2</v>
+        <v>0.04766979366533508</v>
       </c>
       <c r="E17">
-        <v>5.3393357781594257E-2</v>
+        <v>0.05022177535272598</v>
       </c>
       <c r="F17">
-        <v>7.9283523144220047E-2</v>
+        <v>0.0740774744103242</v>
       </c>
       <c r="G17">
-        <v>7.1968577398212608E-2</v>
+        <v>0.06959321188919554</v>
       </c>
       <c r="H17">
-        <v>9.4001072168497291E-2</v>
+        <v>0.08771042217845504</v>
       </c>
       <c r="I17">
-        <v>0.1020205724689882</v>
+        <v>0.0975378296516124</v>
       </c>
       <c r="J17">
-        <v>0.11314097556498311</v>
+        <v>0.1101749988910397</v>
       </c>
       <c r="K17">
-        <v>0.1329182398327137</v>
+        <v>0.1280482338883004</v>
       </c>
       <c r="L17">
-        <v>0.1387502692569792</v>
+        <v>0.1357271209841751</v>
       </c>
       <c r="M17">
-        <v>0.17676619437012889</v>
+        <v>0.1709245433309673</v>
       </c>
       <c r="N17">
-        <v>0.21616925331274039</v>
+        <v>0.2103275009230217</v>
       </c>
       <c r="O17">
-        <v>0.2520406724855202</v>
+        <v>0.2482967768958136</v>
       </c>
       <c r="P17">
-        <v>0.26281216247890421</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.25783246017304</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>2.0539739106764762E-2</v>
+        <v>0.02061033297029846</v>
       </c>
       <c r="C18">
-        <v>4.7921128123660117E-2</v>
+        <v>0.04838069771069375</v>
       </c>
       <c r="D18">
-        <v>6.3347741798996382E-2</v>
+        <v>0.06289352108418989</v>
       </c>
       <c r="E18">
-        <v>0.10199789541294681</v>
+        <v>0.1000352955361322</v>
       </c>
       <c r="F18">
-        <v>0.11076392385733561</v>
+        <v>0.1104755968941481</v>
       </c>
       <c r="G18">
-        <v>0.1400734500050497</v>
+        <v>0.137771135485897</v>
       </c>
       <c r="H18">
-        <v>0.15632525077181161</v>
+        <v>0.1558326805377068</v>
       </c>
       <c r="I18">
-        <v>0.2051712470405512</v>
+        <v>0.204968800525888</v>
       </c>
       <c r="J18">
-        <v>0.27815208229152127</v>
+        <v>0.2765996305422713</v>
       </c>
       <c r="K18">
-        <v>0.35385047104701778</v>
+        <v>0.3536974930540484</v>
       </c>
       <c r="L18">
-        <v>0.42922287773808859</v>
+        <v>0.4301135900653281</v>
       </c>
       <c r="M18">
-        <v>0.46835730281529231</v>
+        <v>0.4733793605474895</v>
       </c>
       <c r="N18">
-        <v>0.4841861005622265</v>
+        <v>0.4866426106750049</v>
       </c>
       <c r="O18">
-        <v>0.49032053758888872</v>
+        <v>0.4946789746543391</v>
       </c>
       <c r="P18">
-        <v>0.49754983717471479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.5030462441178406</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>1.9384239379676371E-2</v>
+        <v>0.01896591443076634</v>
       </c>
       <c r="C19">
-        <v>4.4244852790760847E-2</v>
+        <v>0.0444080427613599</v>
       </c>
       <c r="D19">
-        <v>5.5500064198107817E-2</v>
+        <v>0.05481907890241167</v>
       </c>
       <c r="E19">
-        <v>8.4141226379288447E-2</v>
+        <v>0.08470993830247853</v>
       </c>
       <c r="F19">
-        <v>8.4096075495863176E-2</v>
+        <v>0.0837181932538742</v>
       </c>
       <c r="G19">
-        <v>0.12374483605363321</v>
+        <v>0.1239780556787815</v>
       </c>
       <c r="H19">
-        <v>0.12879853227469751</v>
+        <v>0.1288929007769558</v>
       </c>
       <c r="I19">
-        <v>0.1669737252159661</v>
+        <v>0.1702752599258546</v>
       </c>
       <c r="J19">
-        <v>0.21433046456609131</v>
+        <v>0.2139907667142472</v>
       </c>
       <c r="K19">
-        <v>0.26591236503537902</v>
+        <v>0.266024844457811</v>
       </c>
       <c r="L19">
-        <v>0.31813067788810601</v>
+        <v>0.3171453219915139</v>
       </c>
       <c r="M19">
-        <v>0.35647370635375419</v>
+        <v>0.3532540274166102</v>
       </c>
       <c r="N19">
-        <v>0.40224354113771771</v>
+        <v>0.3974067218736814</v>
       </c>
       <c r="O19">
-        <v>0.4287213505425182</v>
+        <v>0.4213620981654234</v>
       </c>
       <c r="P19">
-        <v>0.46034018404360411</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4563017956820684</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>1.9131054504578748E-2</v>
+        <v>0.01833321149596756</v>
       </c>
       <c r="C20">
-        <v>3.6489462134885242E-2</v>
+        <v>0.03421185367376478</v>
       </c>
       <c r="D20">
-        <v>5.2734801623036787E-2</v>
+        <v>0.05264119975118964</v>
       </c>
       <c r="E20">
-        <v>8.1278513478414749E-2</v>
+        <v>0.08168591003679504</v>
       </c>
       <c r="F20">
-        <v>7.6958589437227554E-2</v>
+        <v>0.07720906881935463</v>
       </c>
       <c r="G20">
-        <v>8.5758589840205901E-2</v>
+        <v>0.08650603073942376</v>
       </c>
       <c r="H20">
-        <v>0.106160467913576</v>
+        <v>0.1072937978780646</v>
       </c>
       <c r="I20">
-        <v>0.1521747483091116</v>
+        <v>0.1544287518050668</v>
       </c>
       <c r="J20">
-        <v>0.18450188199923859</v>
+        <v>0.1859015557082121</v>
       </c>
       <c r="K20">
-        <v>0.2105457385007414</v>
+        <v>0.2107175076185852</v>
       </c>
       <c r="L20">
-        <v>0.24887722880253521</v>
+        <v>0.2511346142321396</v>
       </c>
       <c r="M20">
-        <v>0.28578967348227552</v>
+        <v>0.2844170226813624</v>
       </c>
       <c r="N20">
-        <v>0.29978983176917978</v>
+        <v>0.2970422422254757</v>
       </c>
       <c r="O20">
-        <v>0.338398922834729</v>
+        <v>0.3324540915964564</v>
       </c>
       <c r="P20">
-        <v>0.37930897126623092</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3686372932553561</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>3.7700900232258083E-2</v>
+        <v>0.04040732143795567</v>
       </c>
       <c r="C21">
-        <v>3.6220223496544857E-2</v>
+        <v>0.03918778581483084</v>
       </c>
       <c r="D21">
-        <v>6.4947460524535927E-2</v>
+        <v>0.07004542667696734</v>
       </c>
       <c r="E21">
-        <v>0.16052813074907971</v>
+        <v>0.1658267680327372</v>
       </c>
       <c r="F21">
-        <v>0.1380570795802829</v>
+        <v>0.1433556169344894</v>
       </c>
       <c r="G21">
-        <v>0.1609841203637348</v>
+        <v>0.1721702243775829</v>
       </c>
       <c r="H21">
-        <v>0.24560562692952981</v>
+        <v>0.2544230998112293</v>
       </c>
       <c r="I21">
-        <v>0.3348810100193656</v>
+        <v>0.3473920332117321</v>
       </c>
       <c r="J21">
-        <v>0.37422050833915721</v>
+        <v>0.3858837838486736</v>
       </c>
       <c r="K21">
-        <v>0.43187800486138261</v>
+        <v>0.4433842252542836</v>
       </c>
       <c r="L21">
-        <v>0.4656185728582522</v>
+        <v>0.4769629171257458</v>
       </c>
       <c r="M21">
-        <v>0.49380984843366421</v>
+        <v>0.5000165366430188</v>
       </c>
       <c r="N21">
-        <v>0.51420838755453335</v>
+        <v>0.5222823644039596</v>
       </c>
       <c r="O21">
-        <v>0.51855378178525502</v>
+        <v>0.5245488323276553</v>
       </c>
       <c r="P21">
-        <v>0.54710996575912541</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.5515231039741333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>3.941483044482913E-2</v>
+        <v>0.04000148219643362</v>
       </c>
       <c r="C22">
-        <v>3.7241382625481163E-2</v>
+        <v>0.03813730969907536</v>
       </c>
       <c r="D22">
-        <v>6.2634150400258659E-2</v>
+        <v>0.06614740163041921</v>
       </c>
       <c r="E22">
-        <v>0.16155371807864011</v>
+        <v>0.1709170096826577</v>
       </c>
       <c r="F22">
-        <v>0.1431356805035883</v>
+        <v>0.1431518405122929</v>
       </c>
       <c r="G22">
-        <v>0.15279867095745939</v>
+        <v>0.1550200404432004</v>
       </c>
       <c r="H22">
-        <v>0.24881335452063519</v>
+        <v>0.2485551353500431</v>
       </c>
       <c r="I22">
-        <v>0.3262512275458922</v>
+        <v>0.3215439743310384</v>
       </c>
       <c r="J22">
-        <v>0.38527053313664428</v>
+        <v>0.3794732629016327</v>
       </c>
       <c r="K22">
-        <v>0.42369134654932689</v>
+        <v>0.4200847220036049</v>
       </c>
       <c r="L22">
-        <v>0.46751904473757738</v>
+        <v>0.4705187177665652</v>
       </c>
       <c r="M22">
-        <v>0.49952557857594421</v>
+        <v>0.502702528709662</v>
       </c>
       <c r="N22">
-        <v>0.4984998583934947</v>
+        <v>0.5084085033224242</v>
       </c>
       <c r="O22">
-        <v>0.50147365112219244</v>
+        <v>0.5138628310917641</v>
       </c>
       <c r="P22">
-        <v>0.5478640862368952</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.5547377942851467</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>2.1810678655214358E-2</v>
+        <v>0.02169893790471511</v>
       </c>
       <c r="C23">
-        <v>3.376030359660076E-2</v>
+        <v>0.03437559378906285</v>
       </c>
       <c r="D23">
-        <v>9.0697528348000711E-2</v>
+        <v>0.09175874955386254</v>
       </c>
       <c r="E23">
-        <v>7.3671027603425254E-2</v>
+        <v>0.07286985222596021</v>
       </c>
       <c r="F23">
-        <v>0.16057762848110829</v>
+        <v>0.1610552069770838</v>
       </c>
       <c r="G23">
-        <v>0.2464753537917371</v>
+        <v>0.2554268221414772</v>
       </c>
       <c r="H23">
-        <v>0.34222050582717112</v>
+        <v>0.3437947090777287</v>
       </c>
       <c r="I23">
-        <v>0.3806337738121171</v>
+        <v>0.3823595178038112</v>
       </c>
       <c r="J23">
-        <v>0.3947458265394736</v>
+        <v>0.3913777395006391</v>
       </c>
       <c r="K23">
-        <v>0.4629749017574572</v>
+        <v>0.461043319187003</v>
       </c>
       <c r="L23">
-        <v>0.51253872434441416</v>
+        <v>0.5109861944474743</v>
       </c>
       <c r="M23">
-        <v>0.54819080559960276</v>
+        <v>0.5511968766833051</v>
       </c>
       <c r="N23">
-        <v>0.59097070455852463</v>
+        <v>0.5902978255447546</v>
       </c>
       <c r="O23">
-        <v>0.61090427466139274</v>
+        <v>0.6109091088500476</v>
       </c>
       <c r="P23">
-        <v>0.65260158011510683</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.654229313496853</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>4.5836375610687742E-2</v>
+        <v>0.02080513651430926</v>
       </c>
       <c r="C24">
-        <v>0.1168985208912261</v>
+        <v>0.03210257210312972</v>
       </c>
       <c r="D24">
-        <v>0.12657278247417331</v>
+        <v>0.07692472195543198</v>
       </c>
       <c r="E24">
-        <v>0.17630606109313929</v>
+        <v>0.06383258868358588</v>
       </c>
       <c r="F24">
-        <v>0.39084731800591449</v>
+        <v>0.0783825803466689</v>
       </c>
       <c r="G24">
-        <v>0.42218057152787319</v>
+        <v>0.09084576223740126</v>
       </c>
       <c r="H24">
-        <v>0.53038815146898832</v>
+        <v>0.1135170750571886</v>
       </c>
       <c r="I24">
-        <v>0.68201393547197586</v>
+        <v>0.1915749228285009</v>
       </c>
       <c r="J24">
-        <v>0.85038517531585633</v>
+        <v>0.2185962245363803</v>
       </c>
       <c r="K24">
-        <v>1.005660970035205</v>
+        <v>0.2529072611119899</v>
       </c>
       <c r="L24">
-        <v>1.059083430600724</v>
+        <v>0.3010809697139009</v>
       </c>
       <c r="M24">
-        <v>1.091542484143772</v>
+        <v>0.3827523267373741</v>
       </c>
       <c r="N24">
-        <v>1.086776276214203</v>
+        <v>0.424940660479125</v>
       </c>
       <c r="O24">
-        <v>1.0817145668842201</v>
+        <v>0.5007781397558642</v>
       </c>
       <c r="P24">
-        <v>1.104796395030945</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.5765833447584525</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>6.9342673346376324E-2</v>
+        <v>0.02083344619995531</v>
       </c>
       <c r="C25">
-        <v>0.13335761195815141</v>
+        <v>0.03195066923455803</v>
       </c>
       <c r="D25">
-        <v>0.1789363259355731</v>
+        <v>0.08019255776298484</v>
       </c>
       <c r="E25">
-        <v>0.27045733539875888</v>
+        <v>0.06740044118986155</v>
       </c>
       <c r="F25">
-        <v>0.35277525778308888</v>
+        <v>0.08671226208301408</v>
       </c>
       <c r="G25">
-        <v>0.50478883549451437</v>
+        <v>0.1269722416151087</v>
       </c>
       <c r="H25">
-        <v>0.66911543800176354</v>
+        <v>0.1634773211167532</v>
       </c>
       <c r="I25">
-        <v>0.83024670742669948</v>
+        <v>0.2169657481061548</v>
       </c>
       <c r="J25">
-        <v>1.029582190861827</v>
+        <v>0.2254582386815287</v>
       </c>
       <c r="K25">
-        <v>1.190304932731381</v>
+        <v>0.2468971610082572</v>
       </c>
       <c r="L25">
-        <v>1.3675941906642699</v>
+        <v>0.2838132946787288</v>
       </c>
       <c r="M25">
-        <v>1.551509854092916</v>
+        <v>0.3417004792980098</v>
       </c>
       <c r="N25">
-        <v>1.6594298673034129</v>
+        <v>0.408479856843477</v>
       </c>
       <c r="O25">
-        <v>1.772940793871892</v>
+        <v>0.4525326349547039</v>
       </c>
       <c r="P25">
-        <v>1.845752328202851</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.5340167974613066</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>4.2019761527461133E-2</v>
+        <v>0.01826124303187071</v>
       </c>
       <c r="C26">
-        <v>8.6679511341316906E-2</v>
+        <v>0.03148571191663452</v>
       </c>
       <c r="D26">
-        <v>8.9352686180260571E-2</v>
+        <v>0.0757530795657847</v>
       </c>
       <c r="E26">
-        <v>0.1163346654249017</v>
+        <v>0.06991091496695645</v>
       </c>
       <c r="F26">
-        <v>0.18442728830972871</v>
+        <v>0.08401243187345697</v>
       </c>
       <c r="G26">
-        <v>0.24875404648562</v>
+        <v>0.09113752246275941</v>
       </c>
       <c r="H26">
-        <v>0.32941911882929559</v>
+        <v>0.1295407791723787</v>
       </c>
       <c r="I26">
-        <v>0.35205863889770123</v>
+        <v>0.1979949189002602</v>
       </c>
       <c r="J26">
-        <v>0.39982669030773937</v>
+        <v>0.2414281012369004</v>
       </c>
       <c r="K26">
-        <v>0.43744117661034038</v>
+        <v>0.2761699201612401</v>
       </c>
       <c r="L26">
-        <v>0.505401415022525</v>
+        <v>0.3434030582589949</v>
       </c>
       <c r="M26">
-        <v>0.56486986407271322</v>
+        <v>0.4016028213029392</v>
       </c>
       <c r="N26">
-        <v>0.67434655692510226</v>
+        <v>0.4747555961070611</v>
       </c>
       <c r="O26">
-        <v>0.695154706700577</v>
+        <v>0.5440375230114866</v>
       </c>
       <c r="P26">
-        <v>0.76405849724141428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.6610970964827654</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>4.7641644709575742E-2</v>
+        <v>0.01819544630677883</v>
       </c>
       <c r="C27">
-        <v>7.9049525013338964E-2</v>
+        <v>0.0319145166402296</v>
       </c>
       <c r="D27">
-        <v>0.1703272322283598</v>
+        <v>0.07395011768255144</v>
       </c>
       <c r="E27">
-        <v>0.13569243105373641</v>
+        <v>0.06813004429859137</v>
       </c>
       <c r="F27">
-        <v>0.21353782670254801</v>
+        <v>0.0779721628986062</v>
       </c>
       <c r="G27">
-        <v>0.33051783471576951</v>
+        <v>0.08154918091369145</v>
       </c>
       <c r="H27">
-        <v>0.40377558046275169</v>
+        <v>0.09640847634327732</v>
       </c>
       <c r="I27">
-        <v>0.50451191967014997</v>
+        <v>0.1256245987324932</v>
       </c>
       <c r="J27">
-        <v>0.55453565648987935</v>
+        <v>0.1370669917337376</v>
       </c>
       <c r="K27">
-        <v>0.58273297994211493</v>
+        <v>0.14481624546686</v>
       </c>
       <c r="L27">
-        <v>0.61487243108994016</v>
+        <v>0.1572331871205016</v>
       </c>
       <c r="M27">
-        <v>0.72528880923035821</v>
+        <v>0.1883800660549068</v>
       </c>
       <c r="N27">
-        <v>0.79869142865729503</v>
+        <v>0.2322955904624474</v>
       </c>
       <c r="O27">
-        <v>0.92419432464279494</v>
+        <v>0.2424733485024071</v>
       </c>
       <c r="P27">
-        <v>1.027354330519235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.3336604242063849</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>2.0100157926440598E-2</v>
+        <v>0.02002311882721797</v>
       </c>
       <c r="C28">
-        <v>3.1404784861044921E-2</v>
+        <v>0.03130131163788685</v>
       </c>
       <c r="D28">
-        <v>7.5591987626138502E-2</v>
+        <v>0.08014158857966391</v>
       </c>
       <c r="E28">
-        <v>6.3432939272812794E-2</v>
+        <v>0.06642886644168322</v>
       </c>
       <c r="F28">
-        <v>7.7443488835566843E-2</v>
+        <v>0.08507578797484405</v>
       </c>
       <c r="G28">
-        <v>8.8968791013139259E-2</v>
+        <v>0.1120043314193457</v>
       </c>
       <c r="H28">
-        <v>0.11639034892552449</v>
+        <v>0.1354678612828211</v>
       </c>
       <c r="I28">
-        <v>0.19161631032303089</v>
+        <v>0.146981022300585</v>
       </c>
       <c r="J28">
-        <v>0.21810029796854871</v>
+        <v>0.1510436669968899</v>
       </c>
       <c r="K28">
-        <v>0.2513751435286069</v>
+        <v>0.1490772947534608</v>
       </c>
       <c r="L28">
-        <v>0.29772577978976922</v>
+        <v>0.1623862038030535</v>
       </c>
       <c r="M28">
-        <v>0.37427072776626491</v>
+        <v>0.1868104828592568</v>
       </c>
       <c r="N28">
-        <v>0.41820017247674368</v>
+        <v>0.2275105950379777</v>
       </c>
       <c r="O28">
-        <v>0.48979975970288753</v>
+        <v>0.2399526407954831</v>
       </c>
       <c r="P28">
-        <v>0.56106225185081671</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.2941237929530945</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>1.938705469320379E-2</v>
+        <v>0.02112941444881189</v>
       </c>
       <c r="C29">
-        <v>3.0857835988044039E-2</v>
+        <v>0.03183376639031521</v>
       </c>
       <c r="D29">
-        <v>7.9147374598806275E-2</v>
+        <v>0.07989227502804364</v>
       </c>
       <c r="E29">
-        <v>6.552893335739407E-2</v>
+        <v>0.06776342531252877</v>
       </c>
       <c r="F29">
-        <v>8.5753997367645551E-2</v>
+        <v>0.08501943447487159</v>
       </c>
       <c r="G29">
-        <v>0.12673407616645449</v>
+        <v>0.1106069020435079</v>
       </c>
       <c r="H29">
-        <v>0.16535319032218301</v>
+        <v>0.1328123516120623</v>
       </c>
       <c r="I29">
-        <v>0.2112972466184154</v>
+        <v>0.1477660310461653</v>
       </c>
       <c r="J29">
-        <v>0.23306854103974711</v>
+        <v>0.1531498676232198</v>
       </c>
       <c r="K29">
-        <v>0.25110671697813353</v>
+        <v>0.1512838093392486</v>
       </c>
       <c r="L29">
-        <v>0.29375685850668842</v>
+        <v>0.1614911255878907</v>
       </c>
       <c r="M29">
-        <v>0.35420084661975509</v>
+        <v>0.1797235705850851</v>
       </c>
       <c r="N29">
-        <v>0.42497156275452352</v>
+        <v>0.2155729244937057</v>
       </c>
       <c r="O29">
-        <v>0.47283340636863802</v>
+        <v>0.2225671730937245</v>
       </c>
       <c r="P29">
-        <v>0.55404395915277127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.2732943009749813</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>1.8425218216366779E-2</v>
+        <v>0.02062377334168819</v>
       </c>
       <c r="C30">
-        <v>3.0872422251360439E-2</v>
+        <v>0.03149190212070707</v>
       </c>
       <c r="D30">
-        <v>7.1784902461499711E-2</v>
+        <v>0.07771390155953295</v>
       </c>
       <c r="E30">
-        <v>6.8212134131020785E-2</v>
+        <v>0.06295470654199264</v>
       </c>
       <c r="F30">
-        <v>8.0506999716136618E-2</v>
+        <v>0.08008851365364589</v>
       </c>
       <c r="G30">
-        <v>9.10758846100862E-2</v>
+        <v>0.1039144611837954</v>
       </c>
       <c r="H30">
-        <v>0.12750681013619489</v>
+        <v>0.1233276264963161</v>
       </c>
       <c r="I30">
-        <v>0.19989314432967981</v>
+        <v>0.1336756894150068</v>
       </c>
       <c r="J30">
-        <v>0.2397495320449374</v>
+        <v>0.1387707425351256</v>
       </c>
       <c r="K30">
-        <v>0.27326094599907369</v>
+        <v>0.142918266321433</v>
       </c>
       <c r="L30">
-        <v>0.33539218377852298</v>
+        <v>0.1515275387152385</v>
       </c>
       <c r="M30">
-        <v>0.39535727081645372</v>
+        <v>0.1667373019942068</v>
       </c>
       <c r="N30">
-        <v>0.46736143943194519</v>
+        <v>0.1996700167760945</v>
       </c>
       <c r="O30">
-        <v>0.53273576004986856</v>
+        <v>0.2078055832627342</v>
       </c>
       <c r="P30">
-        <v>0.6474873021319707</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.2520471756580309</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>1.773734347406164E-2</v>
+        <v>0.01929823480043202</v>
       </c>
       <c r="C31">
-        <v>3.0395525386558431E-2</v>
+        <v>0.03009710807536214</v>
       </c>
       <c r="D31">
-        <v>7.0638893589399898E-2</v>
+        <v>0.07624570362560479</v>
       </c>
       <c r="E31">
-        <v>6.6268737739753059E-2</v>
+        <v>0.06495516520248967</v>
       </c>
       <c r="F31">
-        <v>7.7624518198343817E-2</v>
+        <v>0.08082239979442984</v>
       </c>
       <c r="G31">
-        <v>7.9413532617861882E-2</v>
+        <v>0.1052948135781711</v>
       </c>
       <c r="H31">
-        <v>9.3916417708891919E-2</v>
+        <v>0.1231943795330984</v>
       </c>
       <c r="I31">
-        <v>0.1231644767893175</v>
+        <v>0.137734285918823</v>
       </c>
       <c r="J31">
-        <v>0.13717515905345079</v>
+        <v>0.1461077883506169</v>
       </c>
       <c r="K31">
-        <v>0.1414126455523648</v>
+        <v>0.1430249468059704</v>
       </c>
       <c r="L31">
-        <v>0.15349614936736139</v>
+        <v>0.1521953103559479</v>
       </c>
       <c r="M31">
-        <v>0.18631769103574891</v>
+        <v>0.16495338056376</v>
       </c>
       <c r="N31">
-        <v>0.23187710734620839</v>
+        <v>0.1927719145654072</v>
       </c>
       <c r="O31">
-        <v>0.23784575100474939</v>
+        <v>0.2027076700823992</v>
       </c>
       <c r="P31">
-        <v>0.32791632731639642</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2285606631638551</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>2.06139692856665E-2</v>
+        <v>0.01996753373255833</v>
       </c>
       <c r="C32">
-        <v>3.2006422211794061E-2</v>
+        <v>0.0320689132068277</v>
       </c>
       <c r="D32">
-        <v>8.0574205377066277E-2</v>
+        <v>0.08288888414699824</v>
       </c>
       <c r="E32">
-        <v>6.6090413187850361E-2</v>
+        <v>0.06763637075786511</v>
       </c>
       <c r="F32">
-        <v>8.26879622148875E-2</v>
+        <v>0.08604726340762792</v>
       </c>
       <c r="G32">
-        <v>0.1074936117905312</v>
+        <v>0.1170032986510133</v>
       </c>
       <c r="H32">
-        <v>0.1308037102849515</v>
+        <v>0.1391184807406507</v>
       </c>
       <c r="I32">
-        <v>0.14076054545558339</v>
+        <v>0.1626943389822947</v>
       </c>
       <c r="J32">
-        <v>0.14530477388600341</v>
+        <v>0.1640470289799882</v>
       </c>
       <c r="K32">
-        <v>0.1479833371026289</v>
+        <v>0.1611779531453827</v>
       </c>
       <c r="L32">
-        <v>0.16105789065927351</v>
+        <v>0.176271082328972</v>
       </c>
       <c r="M32">
-        <v>0.18089858094034339</v>
+        <v>0.2106101213423077</v>
       </c>
       <c r="N32">
-        <v>0.2213453775542423</v>
+        <v>0.2565020750101359</v>
       </c>
       <c r="O32">
-        <v>0.23732656395772919</v>
+        <v>0.2597353653047222</v>
       </c>
       <c r="P32">
-        <v>0.28908842022928721</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.3017756517328318</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>2.114149251389907E-2</v>
+        <v>0.01977728053959493</v>
       </c>
       <c r="C33">
-        <v>3.0989896883784399E-2</v>
+        <v>0.03124329670041059</v>
       </c>
       <c r="D33">
-        <v>7.8276414834348107E-2</v>
+        <v>0.07781828958833736</v>
       </c>
       <c r="E33">
-        <v>6.6613610995768124E-2</v>
+        <v>0.06570392310415041</v>
       </c>
       <c r="F33">
-        <v>8.360702095526551E-2</v>
+        <v>0.08350202673451934</v>
       </c>
       <c r="G33">
-        <v>0.110549357111474</v>
+        <v>0.1139663443611888</v>
       </c>
       <c r="H33">
-        <v>0.13095634952970031</v>
+        <v>0.1384173060355014</v>
       </c>
       <c r="I33">
-        <v>0.14704437780900931</v>
+        <v>0.1571946156667655</v>
       </c>
       <c r="J33">
-        <v>0.15204052768348661</v>
+        <v>0.1571196176118937</v>
       </c>
       <c r="K33">
-        <v>0.14800144992194</v>
+        <v>0.1549639597229878</v>
       </c>
       <c r="L33">
-        <v>0.1564073617101652</v>
+        <v>0.1667007130322703</v>
       </c>
       <c r="M33">
-        <v>0.17530403471530939</v>
+        <v>0.1978037448314267</v>
       </c>
       <c r="N33">
-        <v>0.2117645664164248</v>
+        <v>0.2419238591054714</v>
       </c>
       <c r="O33">
-        <v>0.22138922664129251</v>
+        <v>0.2486787408344469</v>
       </c>
       <c r="P33">
-        <v>0.26858885885927819</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2875166593012987</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>2.181345896328701E-2</v>
+        <v>0.02148447267110154</v>
       </c>
       <c r="C34">
-        <v>3.3433721113053871E-2</v>
+        <v>0.03240002974688028</v>
       </c>
       <c r="D34">
-        <v>8.2257271557590883E-2</v>
+        <v>0.08151827991565064</v>
       </c>
       <c r="E34">
-        <v>7.1412682840639841E-2</v>
+        <v>0.06788820287366171</v>
       </c>
       <c r="F34">
-        <v>8.7814557428353535E-2</v>
+        <v>0.08547364258387258</v>
       </c>
       <c r="G34">
-        <v>0.11334607282747081</v>
+        <v>0.1107739685990066</v>
       </c>
       <c r="H34">
-        <v>0.1337593199277971</v>
+        <v>0.1336685967032791</v>
       </c>
       <c r="I34">
-        <v>0.14691641767334571</v>
+        <v>0.1515665731737104</v>
       </c>
       <c r="J34">
-        <v>0.14878787997537629</v>
+        <v>0.1544124078061511</v>
       </c>
       <c r="K34">
-        <v>0.14972345213214039</v>
+        <v>0.1493870134015326</v>
       </c>
       <c r="L34">
-        <v>0.15689350181345679</v>
+        <v>0.164299034067115</v>
       </c>
       <c r="M34">
-        <v>0.17611881122968021</v>
+        <v>0.1938730838454632</v>
       </c>
       <c r="N34">
-        <v>0.2067640029009834</v>
+        <v>0.2344255110991078</v>
       </c>
       <c r="O34">
-        <v>0.2155245730530205</v>
+        <v>0.2356449581962731</v>
       </c>
       <c r="P34">
-        <v>0.25585290468361571</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2773761123057999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>2.085613914930684E-2</v>
+        <v>0.01967464567505151</v>
       </c>
       <c r="C35">
-        <v>3.1203428963489929E-2</v>
+        <v>0.0302832011309454</v>
       </c>
       <c r="D35">
-        <v>7.7576892042601209E-2</v>
+        <v>0.0765432750205306</v>
       </c>
       <c r="E35">
-        <v>6.5838618582677366E-2</v>
+        <v>0.06567539394162103</v>
       </c>
       <c r="F35">
-        <v>8.3528768646626617E-2</v>
+        <v>0.08130097457093255</v>
       </c>
       <c r="G35">
-        <v>0.1110132867447904</v>
+        <v>0.1080415920397886</v>
       </c>
       <c r="H35">
-        <v>0.13037401374457591</v>
+        <v>0.126432013231972</v>
       </c>
       <c r="I35">
-        <v>0.14206412052810591</v>
+        <v>0.1455584864546559</v>
       </c>
       <c r="J35">
-        <v>0.14902358963825391</v>
+        <v>0.1534687612444318</v>
       </c>
       <c r="K35">
-        <v>0.14679579638860929</v>
+        <v>0.1494055894911734</v>
       </c>
       <c r="L35">
-        <v>0.15626672441922521</v>
+        <v>0.1591320001023731</v>
       </c>
       <c r="M35">
-        <v>0.16704907346858239</v>
+        <v>0.1827897386214441</v>
       </c>
       <c r="N35">
-        <v>0.19410784074521559</v>
+        <v>0.2210414580728384</v>
       </c>
       <c r="O35">
-        <v>0.2016389609484297</v>
+        <v>0.2228928739909924</v>
       </c>
       <c r="P35">
-        <v>0.23041191912868539</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2565800981229915</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>2.0813062718108791E-2</v>
+        <v>0.02023881578138964</v>
       </c>
       <c r="C36">
-        <v>3.1606636482475192E-2</v>
+        <v>0.03081182537576022</v>
       </c>
       <c r="D36">
-        <v>7.8003624994584797E-2</v>
+        <v>0.07826815422334898</v>
       </c>
       <c r="E36">
-        <v>6.5271856390368033E-2</v>
+        <v>0.06631148293204026</v>
       </c>
       <c r="F36">
-        <v>8.2545457093948338E-2</v>
+        <v>0.0823325039124756</v>
       </c>
       <c r="G36">
-        <v>0.1081689117172082</v>
+        <v>0.1074029712225336</v>
       </c>
       <c r="H36">
-        <v>0.13219678067961241</v>
+        <v>0.1295384296352978</v>
       </c>
       <c r="I36">
-        <v>0.15273738735796549</v>
+        <v>0.1427013271685033</v>
       </c>
       <c r="J36">
-        <v>0.16153409273414299</v>
+        <v>0.1475882570168116</v>
       </c>
       <c r="K36">
-        <v>0.15690596715611929</v>
+        <v>0.1456273479212731</v>
       </c>
       <c r="L36">
-        <v>0.17138204397885551</v>
+        <v>0.1556827712226958</v>
       </c>
       <c r="M36">
-        <v>0.20326043650087181</v>
+        <v>0.1679721070164617</v>
       </c>
       <c r="N36">
-        <v>0.24947685194099711</v>
+        <v>0.1992008300652812</v>
       </c>
       <c r="O36">
-        <v>0.25178492480397491</v>
+        <v>0.2046979749795537</v>
       </c>
       <c r="P36">
-        <v>0.29595631089369989</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2272247498776424</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>2.017713175905567E-2</v>
+        <v>0.01714625030484351</v>
       </c>
       <c r="C37">
-        <v>3.1231786124048529E-2</v>
+        <v>0.04286033911237086</v>
       </c>
       <c r="D37">
-        <v>7.78980948070781E-2</v>
+        <v>0.0845413985245671</v>
       </c>
       <c r="E37">
-        <v>6.5485698582931295E-2</v>
+        <v>0.1049310532260167</v>
       </c>
       <c r="F37">
-        <v>8.2176302906483145E-2</v>
+        <v>0.1664965062991327</v>
       </c>
       <c r="G37">
-        <v>0.1091284298285745</v>
+        <v>0.2353564354982173</v>
       </c>
       <c r="H37">
-        <v>0.13165471966708239</v>
+        <v>0.24508189405367</v>
       </c>
       <c r="I37">
-        <v>0.14911604621415531</v>
+        <v>0.2696097958777723</v>
       </c>
       <c r="J37">
-        <v>0.15437858571815899</v>
+        <v>0.2927500862530757</v>
       </c>
       <c r="K37">
-        <v>0.15179243963045369</v>
+        <v>0.3401689397269709</v>
       </c>
       <c r="L37">
-        <v>0.16899501032491709</v>
+        <v>0.3970999317909497</v>
       </c>
       <c r="M37">
-        <v>0.19500872124543511</v>
+        <v>0.4650437323464031</v>
       </c>
       <c r="N37">
-        <v>0.2364753171297834</v>
+        <v>0.5661267147949427</v>
       </c>
       <c r="O37">
-        <v>0.24093809796300361</v>
+        <v>0.6305335170913522</v>
       </c>
       <c r="P37">
-        <v>0.27757082643813069</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.6930852089578196</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>2.0247274103130208E-2</v>
+        <v>0.01894879783650438</v>
       </c>
       <c r="C38">
-        <v>3.1127916964105769E-2</v>
+        <v>0.03685986514368012</v>
       </c>
       <c r="D38">
-        <v>7.6876685927370514E-2</v>
+        <v>0.06558438931071486</v>
       </c>
       <c r="E38">
-        <v>6.5687360050236232E-2</v>
+        <v>0.07841477086454196</v>
       </c>
       <c r="F38">
-        <v>8.3530626145346898E-2</v>
+        <v>0.1055666750852209</v>
       </c>
       <c r="G38">
-        <v>0.1116024201820514</v>
+        <v>0.1385830919341297</v>
       </c>
       <c r="H38">
-        <v>0.13365031026268739</v>
+        <v>0.1546729575616694</v>
       </c>
       <c r="I38">
-        <v>0.14941963262649599</v>
+        <v>0.207788627750457</v>
       </c>
       <c r="J38">
-        <v>0.15155962223020769</v>
+        <v>0.2844877081238915</v>
       </c>
       <c r="K38">
-        <v>0.1465357637976771</v>
+        <v>0.3463130798783871</v>
       </c>
       <c r="L38">
-        <v>0.15823696635800019</v>
+        <v>0.3792651943358073</v>
       </c>
       <c r="M38">
-        <v>0.18504320823998369</v>
+        <v>0.3621608975065498</v>
       </c>
       <c r="N38">
-        <v>0.22708473718784389</v>
+        <v>0.3591546913990469</v>
       </c>
       <c r="O38">
-        <v>0.22722244077458079</v>
+        <v>0.3873868268243437</v>
       </c>
       <c r="P38">
-        <v>0.26506094209788272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.415423679096049</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>2.0897314723638091E-2</v>
+        <v>0.01841219200582167</v>
       </c>
       <c r="C39">
-        <v>3.196769342386041E-2</v>
+        <v>0.03782117483614134</v>
       </c>
       <c r="D39">
-        <v>8.0008959907379662E-2</v>
+        <v>0.06249407077320479</v>
       </c>
       <c r="E39">
-        <v>6.6984674859697724E-2</v>
+        <v>0.07665054319223175</v>
       </c>
       <c r="F39">
-        <v>8.3872603047691396E-2</v>
+        <v>0.1031161373950579</v>
       </c>
       <c r="G39">
-        <v>0.11111509621605591</v>
+        <v>0.1332803285254405</v>
       </c>
       <c r="H39">
-        <v>0.1350249064264023</v>
+        <v>0.1318977863543245</v>
       </c>
       <c r="I39">
-        <v>0.15422628987453971</v>
+        <v>0.1672246477307291</v>
       </c>
       <c r="J39">
-        <v>0.15728769080620941</v>
+        <v>0.2557080442762132</v>
       </c>
       <c r="K39">
-        <v>0.14947281180042959</v>
+        <v>0.2977159308785214</v>
       </c>
       <c r="L39">
-        <v>0.1612813490129604</v>
+        <v>0.318301426072749</v>
       </c>
       <c r="M39">
-        <v>0.19182953923090351</v>
+        <v>0.3455678248454498</v>
       </c>
       <c r="N39">
-        <v>0.22791841781974381</v>
+        <v>0.3570423408923739</v>
       </c>
       <c r="O39">
-        <v>0.23017179893061959</v>
+        <v>0.3666960617645641</v>
       </c>
       <c r="P39">
-        <v>0.26198006296659132</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4175437306723825</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>1.9176992815742588E-2</v>
+        <v>0.02617432912804174</v>
       </c>
       <c r="C40">
-        <v>3.1483098445273187E-2</v>
+        <v>0.04759081798554277</v>
       </c>
       <c r="D40">
-        <v>8.2411206380285873E-2</v>
+        <v>0.1090287766024982</v>
       </c>
       <c r="E40">
-        <v>6.8979147966873433E-2</v>
+        <v>0.1092888085977682</v>
       </c>
       <c r="F40">
-        <v>8.5158101698448951E-2</v>
+        <v>0.1286027062062347</v>
       </c>
       <c r="G40">
-        <v>0.1093518699886398</v>
+        <v>0.176746185567731</v>
       </c>
       <c r="H40">
-        <v>0.12914795508571769</v>
+        <v>0.242257775603456</v>
       </c>
       <c r="I40">
-        <v>0.14100044345437421</v>
+        <v>0.298277346518429</v>
       </c>
       <c r="J40">
-        <v>0.15038078882597511</v>
+        <v>0.3335361392902754</v>
       </c>
       <c r="K40">
-        <v>0.1475761248728453</v>
+        <v>0.3663144003081769</v>
       </c>
       <c r="L40">
-        <v>0.15537903414569981</v>
+        <v>0.421163151575341</v>
       </c>
       <c r="M40">
-        <v>0.17058814319930179</v>
+        <v>0.5163345323784716</v>
       </c>
       <c r="N40">
-        <v>0.19719666993193671</v>
+        <v>0.632528841868536</v>
       </c>
       <c r="O40">
-        <v>0.203178748898765</v>
+        <v>0.7415477564839774</v>
       </c>
       <c r="P40">
-        <v>0.22453343930937431</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.8025693375697041</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>1.8170306105706469E-2</v>
+        <v>0.03161782145547021</v>
       </c>
       <c r="C41">
-        <v>4.1533614676496973E-2</v>
+        <v>0.05157383979085461</v>
       </c>
       <c r="D41">
-        <v>8.2902188251708253E-2</v>
+        <v>0.1699489790214497</v>
       </c>
       <c r="E41">
-        <v>0.10493488951893951</v>
+        <v>0.2147884345347844</v>
       </c>
       <c r="F41">
-        <v>0.1660220121405025</v>
+        <v>0.2342525084049171</v>
       </c>
       <c r="G41">
-        <v>0.23689993942979809</v>
+        <v>0.3101283745457932</v>
       </c>
       <c r="H41">
-        <v>0.2461120983322532</v>
+        <v>0.3393160691683297</v>
       </c>
       <c r="I41">
-        <v>0.27196171957389448</v>
+        <v>0.3569585542092565</v>
       </c>
       <c r="J41">
-        <v>0.29906077577006768</v>
+        <v>0.3989731798145776</v>
       </c>
       <c r="K41">
-        <v>0.34349765045653607</v>
+        <v>0.4398258548446496</v>
       </c>
       <c r="L41">
-        <v>0.39819858933500668</v>
+        <v>0.5119037447328378</v>
       </c>
       <c r="M41">
-        <v>0.46631060780238448</v>
+        <v>0.6251318060321897</v>
       </c>
       <c r="N41">
-        <v>0.57003508263571678</v>
+        <v>0.6745298648235388</v>
       </c>
       <c r="O41">
-        <v>0.63420640167297404</v>
+        <v>0.7239448462466471</v>
       </c>
       <c r="P41">
-        <v>0.69902774433154413</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.7597763628142187</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>1.7869540552223891E-2</v>
+        <v>0.04215093774759604</v>
       </c>
       <c r="C42">
-        <v>3.5436181428718183E-2</v>
+        <v>0.04099427888624652</v>
       </c>
       <c r="D42">
-        <v>6.7618449847532625E-2</v>
+        <v>0.1020285778412703</v>
       </c>
       <c r="E42">
-        <v>7.9514876326910566E-2</v>
+        <v>0.2005775430591527</v>
       </c>
       <c r="F42">
-        <v>0.1057995477930076</v>
+        <v>0.2074590390947044</v>
       </c>
       <c r="G42">
-        <v>0.1370231459131962</v>
+        <v>0.2058009321605099</v>
       </c>
       <c r="H42">
-        <v>0.15282482673445599</v>
+        <v>0.2421257968570887</v>
       </c>
       <c r="I42">
-        <v>0.20983947211848811</v>
+        <v>0.3169510550180039</v>
       </c>
       <c r="J42">
-        <v>0.28818365317723882</v>
+        <v>0.4195410501682345</v>
       </c>
       <c r="K42">
-        <v>0.35100796204038048</v>
+        <v>0.4861341574596031</v>
       </c>
       <c r="L42">
-        <v>0.38292421653767977</v>
+        <v>0.5424382700906034</v>
       </c>
       <c r="M42">
-        <v>0.3637430605767884</v>
+        <v>0.5968380434276007</v>
       </c>
       <c r="N42">
-        <v>0.36166148047003399</v>
+        <v>0.6296824837422634</v>
       </c>
       <c r="O42">
-        <v>0.39233091967314182</v>
+        <v>0.683487191627711</v>
       </c>
       <c r="P42">
-        <v>0.41933472785458809</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.7465284595094752</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>1.6463841993308859E-2</v>
+        <v>0.02305367186670204</v>
       </c>
       <c r="C43">
-        <v>3.3146401204700249E-2</v>
+        <v>0.0717290488915332</v>
       </c>
       <c r="D43">
-        <v>6.1082949647376039E-2</v>
+        <v>0.1191871567221819</v>
       </c>
       <c r="E43">
-        <v>7.4913402306769683E-2</v>
+        <v>0.1341548657550802</v>
       </c>
       <c r="F43">
-        <v>0.1010253803736363</v>
+        <v>0.2071920291726627</v>
       </c>
       <c r="G43">
-        <v>0.12971441963723121</v>
+        <v>0.2325183224884243</v>
       </c>
       <c r="H43">
-        <v>0.12865866275156901</v>
+        <v>0.2836957229409972</v>
       </c>
       <c r="I43">
-        <v>0.16452962817145739</v>
+        <v>0.3179998624180502</v>
       </c>
       <c r="J43">
-        <v>0.25051046238487978</v>
+        <v>0.3803570117690634</v>
       </c>
       <c r="K43">
-        <v>0.29086354646559232</v>
+        <v>0.467945269594372</v>
       </c>
       <c r="L43">
-        <v>0.31420109306034538</v>
+        <v>0.5446631581758561</v>
       </c>
       <c r="M43">
-        <v>0.33751731482856412</v>
+        <v>0.6084211007676888</v>
       </c>
       <c r="N43">
-        <v>0.34669957453235312</v>
+        <v>0.6384982924785105</v>
       </c>
       <c r="O43">
-        <v>0.35586708017893492</v>
+        <v>0.6536365342669687</v>
       </c>
       <c r="P43">
-        <v>0.41019790182589572</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>2.647620488376146E-2</v>
-      </c>
-      <c r="C44">
-        <v>4.4889169908363891E-2</v>
-      </c>
-      <c r="D44">
-        <v>0.1045943883100361</v>
-      </c>
-      <c r="E44">
-        <v>0.1041805018649964</v>
-      </c>
-      <c r="F44">
-        <v>0.12709492668885369</v>
-      </c>
-      <c r="G44">
-        <v>0.17055660434448799</v>
-      </c>
-      <c r="H44">
-        <v>0.23262635085030481</v>
-      </c>
-      <c r="I44">
-        <v>0.28930821181617622</v>
-      </c>
-      <c r="J44">
-        <v>0.32569626140271429</v>
-      </c>
-      <c r="K44">
-        <v>0.35886081345172011</v>
-      </c>
-      <c r="L44">
-        <v>0.41412180229952927</v>
-      </c>
-      <c r="M44">
-        <v>0.50205398161310821</v>
-      </c>
-      <c r="N44">
-        <v>0.61532783153173332</v>
-      </c>
-      <c r="O44">
-        <v>0.71627307882266755</v>
-      </c>
-      <c r="P44">
-        <v>0.77520745473832553</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>3.2693653896679553E-2</v>
-      </c>
-      <c r="C45">
-        <v>5.4133089074558827E-2</v>
-      </c>
-      <c r="D45">
-        <v>0.1732426851492341</v>
-      </c>
-      <c r="E45">
-        <v>0.21732487742838449</v>
-      </c>
-      <c r="F45">
-        <v>0.23512767172505561</v>
-      </c>
-      <c r="G45">
-        <v>0.30375821386200552</v>
-      </c>
-      <c r="H45">
-        <v>0.33403263565233282</v>
-      </c>
-      <c r="I45">
-        <v>0.35778456246881768</v>
-      </c>
-      <c r="J45">
-        <v>0.40034983013132253</v>
-      </c>
-      <c r="K45">
-        <v>0.43741702246906222</v>
-      </c>
-      <c r="L45">
-        <v>0.509946418437772</v>
-      </c>
-      <c r="M45">
-        <v>0.61985089043244579</v>
-      </c>
-      <c r="N45">
-        <v>0.668573506761722</v>
-      </c>
-      <c r="O45">
-        <v>0.72056283762118578</v>
-      </c>
-      <c r="P45">
-        <v>0.75939442854593475</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>4.1201326161696139E-2</v>
-      </c>
-      <c r="C46">
-        <v>4.1928197436166381E-2</v>
-      </c>
-      <c r="D46">
-        <v>0.1037779692160431</v>
-      </c>
-      <c r="E46">
-        <v>0.2042898596972289</v>
-      </c>
-      <c r="F46">
-        <v>0.21457015083095199</v>
-      </c>
-      <c r="G46">
-        <v>0.20782238307781301</v>
-      </c>
-      <c r="H46">
-        <v>0.2429544585321487</v>
-      </c>
-      <c r="I46">
-        <v>0.32075366229231389</v>
-      </c>
-      <c r="J46">
-        <v>0.42087649501816121</v>
-      </c>
-      <c r="K46">
-        <v>0.48812635532474358</v>
-      </c>
-      <c r="L46">
-        <v>0.55063348623158648</v>
-      </c>
-      <c r="M46">
-        <v>0.60165168692189397</v>
-      </c>
-      <c r="N46">
-        <v>0.63391068940755224</v>
-      </c>
-      <c r="O46">
-        <v>0.69015342500743748</v>
-      </c>
-      <c r="P46">
-        <v>0.75099347484573808</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>2.3298799256052272E-2</v>
-      </c>
-      <c r="C47">
-        <v>7.2337671727419228E-2</v>
-      </c>
-      <c r="D47">
-        <v>0.1188097031442039</v>
-      </c>
-      <c r="E47">
-        <v>0.132767188474015</v>
-      </c>
-      <c r="F47">
-        <v>0.2035605555555805</v>
-      </c>
-      <c r="G47">
-        <v>0.23056754184333789</v>
-      </c>
-      <c r="H47">
-        <v>0.27810712845922553</v>
-      </c>
-      <c r="I47">
-        <v>0.31422013238856911</v>
-      </c>
-      <c r="J47">
-        <v>0.37327304288477092</v>
-      </c>
-      <c r="K47">
-        <v>0.45894027699178208</v>
-      </c>
-      <c r="L47">
-        <v>0.53969961121071386</v>
-      </c>
-      <c r="M47">
-        <v>0.59875507276087625</v>
-      </c>
-      <c r="N47">
-        <v>0.62863888794634193</v>
-      </c>
-      <c r="O47">
-        <v>0.64343676774002989</v>
-      </c>
-      <c r="P47">
-        <v>0.66926984584770555</v>
+        <v>0.6772850501022272</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>